--- a/data/raw/inventory/Week 33/Audio_Array/Vendor SOH (SP-API).xlsx
+++ b/data/raw/inventory/Week 33/Audio_Array/Vendor SOH (SP-API).xlsx
@@ -67,1285 +67,1297 @@
     <t>SnapshotDate</t>
   </si>
   <si>
+    <t>FBA76727</t>
+  </si>
+  <si>
+    <t>FBA75681</t>
+  </si>
+  <si>
+    <t>FBA79972</t>
+  </si>
+  <si>
+    <t>FBA75679</t>
+  </si>
+  <si>
+    <t>FBA78204</t>
+  </si>
+  <si>
+    <t>FBA75691</t>
+  </si>
+  <si>
+    <t>FBA79839</t>
+  </si>
+  <si>
+    <t>FBA79655</t>
+  </si>
+  <si>
+    <t>FBA75684</t>
+  </si>
+  <si>
+    <t>FBA79980</t>
+  </si>
+  <si>
+    <t>FBA79825</t>
+  </si>
+  <si>
+    <t>FBA79822</t>
+  </si>
+  <si>
+    <t>FBA79010</t>
+  </si>
+  <si>
+    <t>FBA79356</t>
+  </si>
+  <si>
+    <t>FBA76414</t>
+  </si>
+  <si>
+    <t>FBA79957</t>
+  </si>
+  <si>
+    <t>FBA79906</t>
+  </si>
+  <si>
+    <t>FBA78206</t>
+  </si>
+  <si>
+    <t>FBA79996</t>
+  </si>
+  <si>
+    <t>FBA79966</t>
+  </si>
+  <si>
+    <t>FBA79832</t>
+  </si>
+  <si>
+    <t>FBA79904</t>
+  </si>
+  <si>
+    <t>FBA79845</t>
+  </si>
+  <si>
+    <t>FBA75680</t>
+  </si>
+  <si>
+    <t>FBA79908</t>
+  </si>
+  <si>
+    <t>FBA79831</t>
+  </si>
+  <si>
+    <t>FBA79230</t>
+  </si>
+  <si>
+    <t>FBA79813</t>
+  </si>
+  <si>
+    <t>FBA80010</t>
+  </si>
+  <si>
+    <t>FBA79844</t>
+  </si>
+  <si>
+    <t>FBA79962</t>
+  </si>
+  <si>
+    <t>FBA79965</t>
+  </si>
+  <si>
+    <t>FBA76723</t>
+  </si>
+  <si>
+    <t>FBA75678</t>
+  </si>
+  <si>
+    <t>FBA79907</t>
+  </si>
+  <si>
+    <t>FBA79654</t>
+  </si>
+  <si>
+    <t>FBA79841</t>
+  </si>
+  <si>
+    <t>FBA75687</t>
+  </si>
+  <si>
+    <t>FBA76722</t>
+  </si>
+  <si>
+    <t>FBA78961</t>
+  </si>
+  <si>
+    <t>FBA79064</t>
+  </si>
+  <si>
+    <t>FBA79826</t>
+  </si>
+  <si>
+    <t>FBA77171</t>
+  </si>
+  <si>
+    <t>FBA78975</t>
+  </si>
+  <si>
+    <t>FBA79005</t>
+  </si>
+  <si>
+    <t>FBA79104</t>
+  </si>
+  <si>
+    <t>FBA79109</t>
+  </si>
+  <si>
+    <t>FBA79824</t>
+  </si>
+  <si>
+    <t>FBA79981</t>
+  </si>
+  <si>
+    <t>FBA79842</t>
+  </si>
+  <si>
+    <t>FBA79708</t>
+  </si>
+  <si>
+    <t>FBA79016</t>
+  </si>
+  <si>
+    <t>FBA75683</t>
+  </si>
+  <si>
+    <t>FBA78976</t>
+  </si>
+  <si>
+    <t>FBA79909</t>
+  </si>
+  <si>
+    <t>FBA75689</t>
+  </si>
+  <si>
+    <t>FBA79821</t>
+  </si>
+  <si>
+    <t>FBA78960</t>
+  </si>
+  <si>
+    <t>FBA79827</t>
+  </si>
+  <si>
+    <t>FBA79444</t>
+  </si>
+  <si>
+    <t>FBA79105</t>
+  </si>
+  <si>
+    <t>FBA79968</t>
+  </si>
+  <si>
+    <t>FBA79960</t>
+  </si>
+  <si>
+    <t>FBA79011</t>
+  </si>
+  <si>
+    <t>FBA75690</t>
+  </si>
+  <si>
+    <t>FBA80016</t>
+  </si>
+  <si>
+    <t>FBA76728</t>
+  </si>
+  <si>
+    <t>FBA79961</t>
+  </si>
+  <si>
+    <t>FBA75673</t>
+  </si>
+  <si>
+    <t>FBA79846</t>
+  </si>
+  <si>
+    <t>FBA79482</t>
+  </si>
+  <si>
+    <t>FBA80004</t>
+  </si>
+  <si>
+    <t>FBA80007</t>
+  </si>
+  <si>
+    <t>FBA79995</t>
+  </si>
+  <si>
+    <t>FBA79958</t>
+  </si>
+  <si>
+    <t>FBA80009</t>
+  </si>
+  <si>
+    <t>FBA78925</t>
+  </si>
+  <si>
+    <t>FBA79446</t>
+  </si>
+  <si>
+    <t>FBA79815</t>
+  </si>
+  <si>
+    <t>FBA79820</t>
+  </si>
+  <si>
+    <t>FBA79653</t>
+  </si>
+  <si>
+    <t>FBA80005</t>
+  </si>
+  <si>
+    <t>FBA79465</t>
+  </si>
+  <si>
+    <t>FBA79830</t>
+  </si>
+  <si>
+    <t>FBA79838</t>
+  </si>
+  <si>
+    <t>FBA78974</t>
+  </si>
+  <si>
+    <t>FBA79379</t>
+  </si>
+  <si>
+    <t>FBA79836</t>
+  </si>
+  <si>
+    <t>FBA76597</t>
+  </si>
+  <si>
+    <t>FBA80002</t>
+  </si>
+  <si>
+    <t>FBA80085</t>
+  </si>
+  <si>
+    <t>FBA79964</t>
+  </si>
+  <si>
+    <t>FBK79009</t>
+  </si>
+  <si>
+    <t>FBA78973</t>
+  </si>
+  <si>
+    <t>FBA79959</t>
+  </si>
+  <si>
+    <t>FBA79840</t>
+  </si>
+  <si>
+    <t>FBA75675</t>
+  </si>
+  <si>
+    <t>FBA79008</t>
+  </si>
+  <si>
+    <t>FBA76730</t>
+  </si>
+  <si>
+    <t>FBA79447</t>
+  </si>
+  <si>
+    <t>FBA75676</t>
+  </si>
+  <si>
+    <t>FBA75692</t>
+  </si>
+  <si>
+    <t>FBA79835</t>
+  </si>
+  <si>
+    <t>FBA79106</t>
+  </si>
+  <si>
+    <t>FBA79848</t>
+  </si>
+  <si>
+    <t>FBA79979</t>
+  </si>
+  <si>
+    <t>FBK79010</t>
+  </si>
+  <si>
+    <t>FBA79355</t>
+  </si>
+  <si>
     <t>FBA79834</t>
   </si>
   <si>
-    <t>FBK79009</t>
-  </si>
-  <si>
     <t>FBA79009</t>
   </si>
   <si>
+    <t>FBA75674</t>
+  </si>
+  <si>
+    <t>FBA79816</t>
+  </si>
+  <si>
+    <t>FBA76864</t>
+  </si>
+  <si>
+    <t>FBA75686</t>
+  </si>
+  <si>
+    <t>FBA79103</t>
+  </si>
+  <si>
+    <t>FBA79905</t>
+  </si>
+  <si>
+    <t>FBA79448</t>
+  </si>
+  <si>
+    <t>FBA79107</t>
+  </si>
+  <si>
+    <t>FBA79963</t>
+  </si>
+  <si>
+    <t>FBA79847</t>
+  </si>
+  <si>
     <t>FBA79380</t>
   </si>
   <si>
-    <t>FBA79831</t>
-  </si>
-  <si>
-    <t>FBA75681</t>
-  </si>
-  <si>
-    <t>FBA76722</t>
-  </si>
-  <si>
-    <t>FBA76727</t>
-  </si>
-  <si>
-    <t>FBA79444</t>
-  </si>
-  <si>
-    <t>FBA79995</t>
+    <t>FBA79108</t>
+  </si>
+  <si>
+    <t>FBA79449</t>
+  </si>
+  <si>
+    <t>FBA79823</t>
+  </si>
+  <si>
+    <t>FBA78203</t>
+  </si>
+  <si>
+    <t>FBA79694</t>
+  </si>
+  <si>
+    <t>FBA76721</t>
+  </si>
+  <si>
+    <t>FBA76863</t>
+  </si>
+  <si>
+    <t>FBA79982</t>
+  </si>
+  <si>
+    <t>FBA75677</t>
+  </si>
+  <si>
+    <t>FBA79783</t>
+  </si>
+  <si>
+    <t>FBA80084</t>
+  </si>
+  <si>
+    <t>FBA79967</t>
+  </si>
+  <si>
+    <t>FBA75688</t>
+  </si>
+  <si>
+    <t>FBA76862</t>
+  </si>
+  <si>
+    <t>FBA79445</t>
+  </si>
+  <si>
+    <t>FBA79833</t>
+  </si>
+  <si>
+    <t>FBA79722</t>
   </si>
   <si>
     <t>FBA79969</t>
   </si>
   <si>
-    <t>FBA79449</t>
-  </si>
-  <si>
-    <t>FBA79010</t>
-  </si>
-  <si>
-    <t>FBA80002</t>
-  </si>
-  <si>
-    <t>FBA79445</t>
-  </si>
-  <si>
-    <t>FBA79105</t>
-  </si>
-  <si>
-    <t>FBA76723</t>
-  </si>
-  <si>
-    <t>FBA80007</t>
-  </si>
-  <si>
-    <t>FBA79722</t>
-  </si>
-  <si>
-    <t>FBA80004</t>
-  </si>
-  <si>
-    <t>FBA75676</t>
-  </si>
-  <si>
-    <t>FBA75691</t>
-  </si>
-  <si>
-    <t>FBA79008</t>
-  </si>
-  <si>
-    <t>FBA79832</t>
-  </si>
-  <si>
-    <t>FBA79708</t>
-  </si>
-  <si>
-    <t>FBA79815</t>
-  </si>
-  <si>
-    <t>FBA79957</t>
-  </si>
-  <si>
-    <t>FBA79963</t>
-  </si>
-  <si>
-    <t>FBA75690</t>
-  </si>
-  <si>
-    <t>FBA79982</t>
-  </si>
-  <si>
-    <t>FBA78975</t>
-  </si>
-  <si>
-    <t>FBA79355</t>
-  </si>
-  <si>
-    <t>FBA79842</t>
-  </si>
-  <si>
-    <t>FBA79980</t>
-  </si>
-  <si>
-    <t>FBA79653</t>
-  </si>
-  <si>
-    <t>FBA79847</t>
-  </si>
-  <si>
-    <t>FBA79835</t>
-  </si>
-  <si>
-    <t>FBA78960</t>
-  </si>
-  <si>
-    <t>FBA79448</t>
-  </si>
-  <si>
-    <t>FBA78961</t>
-  </si>
-  <si>
-    <t>FBA79823</t>
-  </si>
-  <si>
     <t>FBA80003</t>
   </si>
   <si>
-    <t>FBA80084</t>
-  </si>
-  <si>
-    <t>FBA76730</t>
-  </si>
-  <si>
-    <t>FBA79447</t>
-  </si>
-  <si>
-    <t>FBA79996</t>
-  </si>
-  <si>
-    <t>FBA79103</t>
-  </si>
-  <si>
-    <t>FBA79465</t>
-  </si>
-  <si>
-    <t>FBA79830</t>
-  </si>
-  <si>
-    <t>FBA76863</t>
-  </si>
-  <si>
-    <t>FBA79824</t>
-  </si>
-  <si>
-    <t>FBA80010</t>
-  </si>
-  <si>
-    <t>FBA76862</t>
-  </si>
-  <si>
-    <t>FBA78974</t>
-  </si>
-  <si>
-    <t>FBA79106</t>
-  </si>
-  <si>
-    <t>FBA79848</t>
-  </si>
-  <si>
-    <t>FBA75692</t>
-  </si>
-  <si>
-    <t>FBA79836</t>
-  </si>
-  <si>
-    <t>FBA79064</t>
-  </si>
-  <si>
-    <t>FBA79962</t>
-  </si>
-  <si>
-    <t>FBA76721</t>
-  </si>
-  <si>
-    <t>FBA79816</t>
-  </si>
-  <si>
-    <t>FBA80016</t>
-  </si>
-  <si>
-    <t>FBA79967</t>
-  </si>
-  <si>
-    <t>FBA79826</t>
-  </si>
-  <si>
-    <t>FBA79827</t>
-  </si>
-  <si>
-    <t>FBA79965</t>
-  </si>
-  <si>
-    <t>FBA79909</t>
-  </si>
-  <si>
-    <t>FBA79908</t>
-  </si>
-  <si>
-    <t>FBA79822</t>
-  </si>
-  <si>
-    <t>FBA79108</t>
-  </si>
-  <si>
-    <t>FBA78973</t>
-  </si>
-  <si>
-    <t>FBA79845</t>
-  </si>
-  <si>
-    <t>FBA79820</t>
-  </si>
-  <si>
-    <t>FBA79959</t>
-  </si>
-  <si>
-    <t>FBA78203</t>
-  </si>
-  <si>
-    <t>FBA78925</t>
-  </si>
-  <si>
-    <t>FBA79016</t>
-  </si>
-  <si>
-    <t>FBA79906</t>
-  </si>
-  <si>
-    <t>FBA79838</t>
-  </si>
-  <si>
-    <t>FBA79813</t>
-  </si>
-  <si>
-    <t>FBA79833</t>
-  </si>
-  <si>
-    <t>FBA75677</t>
-  </si>
-  <si>
-    <t>FBA80085</t>
-  </si>
-  <si>
-    <t>FBA79482</t>
-  </si>
-  <si>
-    <t>FBA79821</t>
-  </si>
-  <si>
-    <t>FBA79109</t>
-  </si>
-  <si>
-    <t>FBA75674</t>
-  </si>
-  <si>
-    <t>FBA79972</t>
-  </si>
-  <si>
-    <t>FBA79825</t>
-  </si>
-  <si>
-    <t>FBA79839</t>
-  </si>
-  <si>
-    <t>FBA79966</t>
-  </si>
-  <si>
-    <t>FBA75675</t>
-  </si>
-  <si>
-    <t>FBA79981</t>
-  </si>
-  <si>
-    <t>FBA79907</t>
-  </si>
-  <si>
-    <t>FBA79844</t>
-  </si>
-  <si>
-    <t>FBA79840</t>
-  </si>
-  <si>
-    <t>FBA76864</t>
-  </si>
-  <si>
-    <t>FBA79655</t>
-  </si>
-  <si>
-    <t>FBA79654</t>
-  </si>
-  <si>
-    <t>FBA79961</t>
-  </si>
-  <si>
-    <t>FBA78976</t>
-  </si>
-  <si>
-    <t>FBA79379</t>
-  </si>
-  <si>
-    <t>FBA79356</t>
-  </si>
-  <si>
-    <t>FBA76728</t>
-  </si>
-  <si>
-    <t>FBA79841</t>
-  </si>
-  <si>
-    <t>FBA75679</t>
-  </si>
-  <si>
-    <t>FBA78204</t>
-  </si>
-  <si>
-    <t>FBA79904</t>
-  </si>
-  <si>
-    <t>FBA79104</t>
-  </si>
-  <si>
-    <t>FBA75673</t>
-  </si>
-  <si>
-    <t>FBA79694</t>
-  </si>
-  <si>
-    <t>FBA79958</t>
-  </si>
-  <si>
-    <t>FBA75688</t>
-  </si>
-  <si>
-    <t>FBA79905</t>
-  </si>
-  <si>
-    <t>FBA76597</t>
-  </si>
-  <si>
-    <t>FBA75689</t>
-  </si>
-  <si>
-    <t>FBA76414</t>
-  </si>
-  <si>
-    <t>FBA75680</t>
-  </si>
-  <si>
-    <t>FBA75683</t>
-  </si>
-  <si>
-    <t>FBA79846</t>
-  </si>
-  <si>
-    <t>FBK79010</t>
-  </si>
-  <si>
-    <t>FBA79230</t>
-  </si>
-  <si>
-    <t>FBA79011</t>
-  </si>
-  <si>
-    <t>FBA75687</t>
-  </si>
-  <si>
-    <t>FBA79783</t>
-  </si>
-  <si>
-    <t>FBA79964</t>
-  </si>
-  <si>
-    <t>FBA79107</t>
-  </si>
-  <si>
-    <t>FBA79968</t>
-  </si>
-  <si>
-    <t>FBA79960</t>
-  </si>
-  <si>
-    <t>FBA78206</t>
-  </si>
-  <si>
-    <t>FBA80009</t>
-  </si>
-  <si>
-    <t>FBA77171</t>
-  </si>
-  <si>
-    <t>FBA75684</t>
-  </si>
-  <si>
-    <t>FBA75686</t>
-  </si>
-  <si>
-    <t>FBA79446</t>
-  </si>
-  <si>
-    <t>FBA79005</t>
-  </si>
-  <si>
-    <t>FBA79979</t>
-  </si>
-  <si>
-    <t>FBA75678</t>
-  </si>
-  <si>
-    <t>FBA80005</t>
+    <t>B0BLKCDRNB</t>
+  </si>
+  <si>
+    <t>B0B4FZS38V</t>
+  </si>
+  <si>
+    <t>B0GCP1J2HC</t>
+  </si>
+  <si>
+    <t>B0B4JRQP22</t>
+  </si>
+  <si>
+    <t>B0C4YT43Z3</t>
+  </si>
+  <si>
+    <t>B0B4G5JG4P</t>
+  </si>
+  <si>
+    <t>B0FQBXS6Y2</t>
+  </si>
+  <si>
+    <t>B0DN6PFWNK</t>
+  </si>
+  <si>
+    <t>B0B4G7VWXD</t>
+  </si>
+  <si>
+    <t>B0GN8MMKY1</t>
+  </si>
+  <si>
+    <t>B0FJ2DT13L</t>
+  </si>
+  <si>
+    <t>B0FJ2J6MTF</t>
+  </si>
+  <si>
+    <t>B0CH4T2BJD</t>
+  </si>
+  <si>
+    <t>B0D3Q2T5XX</t>
+  </si>
+  <si>
+    <t>B0BLJVJ2GN</t>
+  </si>
+  <si>
+    <t>B0G3Q517Y2</t>
+  </si>
+  <si>
+    <t>B0FTVVLNS9</t>
+  </si>
+  <si>
+    <t>B0C4YSV3XL</t>
+  </si>
+  <si>
+    <t>B0GW8Z556N</t>
+  </si>
+  <si>
+    <t>B0G53KWRVW</t>
+  </si>
+  <si>
+    <t>B0FJ8S53GW</t>
+  </si>
+  <si>
+    <t>B0FTVQQVDC</t>
+  </si>
+  <si>
+    <t>B0FN7B3KWS</t>
+  </si>
+  <si>
+    <t>B0B4G1PXWV</t>
+  </si>
+  <si>
+    <t>B0FTVV1QJY</t>
+  </si>
+  <si>
+    <t>B0FJ8W5Y9Q</t>
+  </si>
+  <si>
+    <t>B0CX1XK5R6</t>
+  </si>
+  <si>
+    <t>B0FG88HVQ8</t>
+  </si>
+  <si>
+    <t>B0GW8ZQRFK</t>
+  </si>
+  <si>
+    <t>B0FN7DYB2M</t>
+  </si>
+  <si>
+    <t>B0G53LZNY3</t>
+  </si>
+  <si>
+    <t>B0G53PRM34</t>
+  </si>
+  <si>
+    <t>B0BLKF46QG</t>
+  </si>
+  <si>
+    <t>B0B4G8PH2P</t>
+  </si>
+  <si>
+    <t>B0FTVS34SD</t>
+  </si>
+  <si>
+    <t>B0DN6MNS1X</t>
+  </si>
+  <si>
+    <t>B0FQBTRM28</t>
+  </si>
+  <si>
+    <t>B0B4G5ZLTB</t>
+  </si>
+  <si>
+    <t>B0BLKDC4PP</t>
+  </si>
+  <si>
+    <t>B0CBCB9S14</t>
+  </si>
+  <si>
+    <t>B0CJR76Y7G</t>
+  </si>
+  <si>
+    <t>B0FJ2LQT7K</t>
+  </si>
+  <si>
+    <t>B0CH4VCD6R</t>
+  </si>
+  <si>
+    <t>B0CF5TCQKL</t>
+  </si>
+  <si>
+    <t>B0CKHVHVQ1</t>
+  </si>
+  <si>
+    <t>B0CM6NVLT9</t>
+  </si>
+  <si>
+    <t>B0CM9HYVDM</t>
+  </si>
+  <si>
+    <t>B0FJ2K95XT</t>
+  </si>
+  <si>
+    <t>B0GN8MFDGZ</t>
+  </si>
+  <si>
+    <t>B0G4DNF8RZ</t>
+  </si>
+  <si>
+    <t>B0FFB6YJM1</t>
+  </si>
+  <si>
+    <t>B0CH4R1V6S</t>
+  </si>
+  <si>
+    <t>B0B4G94VP3</t>
+  </si>
+  <si>
+    <t>B0CF5SHL15</t>
+  </si>
+  <si>
+    <t>B0FVM17Q4W</t>
+  </si>
+  <si>
+    <t>B0B4G59Y8W</t>
+  </si>
+  <si>
+    <t>B0FJ2JJZL3</t>
+  </si>
+  <si>
+    <t>B0CBCB82MT</t>
+  </si>
+  <si>
+    <t>B0FJ8S5XJ8</t>
+  </si>
+  <si>
+    <t>B0DFMLQBMC</t>
+  </si>
+  <si>
+    <t>B0CM6WH4ZT</t>
+  </si>
+  <si>
+    <t>B0G53M9258</t>
+  </si>
+  <si>
+    <t>B0G3B152FR</t>
+  </si>
+  <si>
+    <t>B0CH4RNWJX</t>
+  </si>
+  <si>
+    <t>B0B4K87PR4</t>
+  </si>
+  <si>
+    <t>B0GKPXQ8G3</t>
+  </si>
+  <si>
+    <t>B0BLNCP74M</t>
+  </si>
+  <si>
+    <t>B0G53H49BS</t>
+  </si>
+  <si>
+    <t>B0B4DPX2J2</t>
+  </si>
+  <si>
+    <t>B0FN7C25VS</t>
+  </si>
+  <si>
+    <t>B0DXFPM4N2</t>
+  </si>
+  <si>
+    <t>B0GW92316G</t>
+  </si>
+  <si>
+    <t>B0GN2LHJY4</t>
+  </si>
+  <si>
+    <t>B0GW8VBCBL</t>
+  </si>
+  <si>
+    <t>B0G3Q59X8C</t>
+  </si>
+  <si>
+    <t>B0GW8R2RYM</t>
+  </si>
+  <si>
+    <t>B0CBC7QMNV</t>
+  </si>
+  <si>
+    <t>B0DFMMTWLY</t>
+  </si>
+  <si>
+    <t>B0FPR7VFCH</t>
+  </si>
+  <si>
+    <t>B0FQJWWDVK</t>
+  </si>
+  <si>
+    <t>B0DN6LJZBR</t>
+  </si>
+  <si>
+    <t>B0GW96CQMG</t>
+  </si>
+  <si>
+    <t>B0DFMQCGT1</t>
+  </si>
+  <si>
+    <t>B0FJ8TSQK1</t>
+  </si>
+  <si>
+    <t>B0FQBX8J17</t>
+  </si>
+  <si>
+    <t>B0CF5RRTDJ</t>
+  </si>
+  <si>
+    <t>B0D3LZWTHV</t>
+  </si>
+  <si>
+    <t>B0FJ8Z1W81</t>
+  </si>
+  <si>
+    <t>B0BQ7H7418</t>
+  </si>
+  <si>
+    <t>B0GW96SHSK</t>
+  </si>
+  <si>
+    <t>B0GXPBHDRF</t>
+  </si>
+  <si>
+    <t>B0G53KWRWH</t>
+  </si>
+  <si>
+    <t>B0FLYHJ6DK</t>
+  </si>
+  <si>
+    <t>B0CF5R3V95</t>
+  </si>
+  <si>
+    <t>B0G39ZHDYP</t>
+  </si>
+  <si>
+    <t>B0FQBWV1ST</t>
+  </si>
+  <si>
+    <t>B0B4G8ZB64</t>
+  </si>
+  <si>
+    <t>B0CH4RT4P8</t>
+  </si>
+  <si>
+    <t>B0BLKB6FRR</t>
+  </si>
+  <si>
+    <t>B0DFMLXD9S</t>
+  </si>
+  <si>
+    <t>B0B4DS678Q</t>
+  </si>
+  <si>
+    <t>B0B4G1HPL5</t>
+  </si>
+  <si>
+    <t>B0FJ8TWCQZ</t>
+  </si>
+  <si>
+    <t>B0CM9KJZWQ</t>
+  </si>
+  <si>
+    <t>B0GN97RFPR</t>
+  </si>
+  <si>
+    <t>B0GN8RQJRG</t>
+  </si>
+  <si>
+    <t>B0FLYJFC22</t>
+  </si>
+  <si>
+    <t>B0D3M86SH1</t>
   </si>
   <si>
     <t>B0FJ8T4WXM</t>
   </si>
   <si>
-    <t>B0FLYHJ6DK</t>
-  </si>
-  <si>
     <t>B0CH4PMR8K</t>
   </si>
   <si>
+    <t>B0B4G19R58</t>
+  </si>
+  <si>
+    <t>B0FPR962YS</t>
+  </si>
+  <si>
+    <t>B0BPLZ5CGV</t>
+  </si>
+  <si>
+    <t>B0B4G89VQJ</t>
+  </si>
+  <si>
+    <t>B0CM6NTWBP</t>
+  </si>
+  <si>
+    <t>B0FTVSH458</t>
+  </si>
+  <si>
+    <t>B0DFMKY4TT</t>
+  </si>
+  <si>
+    <t>B0CM9P5CCK</t>
+  </si>
+  <si>
+    <t>B0G53CB72D</t>
+  </si>
+  <si>
+    <t>B0FN7FYZM3</t>
+  </si>
+  <si>
     <t>B0D3M1B4Z8</t>
   </si>
   <si>
-    <t>B0FJ8W5Y9Q</t>
-  </si>
-  <si>
-    <t>B0B4FZS38V</t>
-  </si>
-  <si>
-    <t>B0BLKDC4PP</t>
-  </si>
-  <si>
-    <t>B0BLKCDRNB</t>
-  </si>
-  <si>
-    <t>B0DFMLQBMC</t>
-  </si>
-  <si>
-    <t>B0GW8VBCBL</t>
+    <t>B0CM9L1QZG</t>
+  </si>
+  <si>
+    <t>B0DFMNGFTD</t>
+  </si>
+  <si>
+    <t>B0FJ2HZCVN</t>
+  </si>
+  <si>
+    <t>B0C4YTNJG7</t>
+  </si>
+  <si>
+    <t>B0DT6T6N6B</t>
+  </si>
+  <si>
+    <t>B0BLKB55BM</t>
+  </si>
+  <si>
+    <t>B0BPM2T7BQ</t>
+  </si>
+  <si>
+    <t>B0GN8MPYPG</t>
+  </si>
+  <si>
+    <t>B0B4KC7VBM</t>
+  </si>
+  <si>
+    <t>B0FF9R3GKK</t>
+  </si>
+  <si>
+    <t>B0GXP97CZG</t>
+  </si>
+  <si>
+    <t>B0G2C2RCXN</t>
+  </si>
+  <si>
+    <t>B0B4G763WS</t>
+  </si>
+  <si>
+    <t>B0BPLWW72Y</t>
+  </si>
+  <si>
+    <t>B0DFMLS8JG</t>
+  </si>
+  <si>
+    <t>B0FJ8PZ9H7</t>
+  </si>
+  <si>
+    <t>B0F2HYY7JF</t>
   </si>
   <si>
     <t>B0G3B677Z5</t>
   </si>
   <si>
-    <t>B0DFMNGFTD</t>
-  </si>
-  <si>
-    <t>B0CH4T2BJD</t>
-  </si>
-  <si>
-    <t>B0GW96SHSK</t>
-  </si>
-  <si>
-    <t>B0DFMLS8JG</t>
-  </si>
-  <si>
-    <t>B0CM6WH4ZT</t>
-  </si>
-  <si>
-    <t>B0BLKF46QG</t>
-  </si>
-  <si>
-    <t>B0GN2LHJY4</t>
-  </si>
-  <si>
-    <t>B0F2HYY7JF</t>
-  </si>
-  <si>
-    <t>B0GW92316G</t>
-  </si>
-  <si>
-    <t>B0B4DS678Q</t>
-  </si>
-  <si>
-    <t>B0B4G5JG4P</t>
-  </si>
-  <si>
-    <t>B0CH4RT4P8</t>
-  </si>
-  <si>
-    <t>B0FJ8S53GW</t>
-  </si>
-  <si>
-    <t>B0FFB6YJM1</t>
-  </si>
-  <si>
-    <t>B0FPR7VFCH</t>
-  </si>
-  <si>
-    <t>B0G3Q517Y2</t>
-  </si>
-  <si>
-    <t>B0G53CB72D</t>
-  </si>
-  <si>
-    <t>B0B4K87PR4</t>
-  </si>
-  <si>
-    <t>B0GN8MPYPG</t>
-  </si>
-  <si>
-    <t>B0CF5TCQKL</t>
-  </si>
-  <si>
-    <t>B0D3M86SH1</t>
-  </si>
-  <si>
-    <t>B0G4DNF8RZ</t>
-  </si>
-  <si>
-    <t>B0GN8MMKY1</t>
-  </si>
-  <si>
-    <t>B0DN6LJZBR</t>
-  </si>
-  <si>
-    <t>B0FN7FYZM3</t>
-  </si>
-  <si>
-    <t>B0FJ8TWCQZ</t>
-  </si>
-  <si>
-    <t>B0CBCB82MT</t>
-  </si>
-  <si>
-    <t>B0DFMKY4TT</t>
-  </si>
-  <si>
-    <t>B0CBCB9S14</t>
-  </si>
-  <si>
-    <t>B0FJ2HZCVN</t>
-  </si>
-  <si>
     <t>B0GW92TTMS</t>
   </si>
   <si>
-    <t>B0GXP97CZG</t>
-  </si>
-  <si>
-    <t>B0BLKB6FRR</t>
-  </si>
-  <si>
-    <t>B0DFMLXD9S</t>
-  </si>
-  <si>
-    <t>B0GW8Z556N</t>
-  </si>
-  <si>
-    <t>B0CM6NTWBP</t>
-  </si>
-  <si>
-    <t>B0DFMQCGT1</t>
-  </si>
-  <si>
-    <t>B0FJ8TSQK1</t>
-  </si>
-  <si>
-    <t>B0BPM2T7BQ</t>
-  </si>
-  <si>
-    <t>B0FJ2K95XT</t>
-  </si>
-  <si>
-    <t>B0GW8ZQRFK</t>
-  </si>
-  <si>
-    <t>B0BPLWW72Y</t>
-  </si>
-  <si>
-    <t>B0CF5RRTDJ</t>
-  </si>
-  <si>
-    <t>B0CM9KJZWQ</t>
-  </si>
-  <si>
-    <t>B0GN97RFPR</t>
-  </si>
-  <si>
-    <t>B0B4G1HPL5</t>
-  </si>
-  <si>
-    <t>B0FJ8Z1W81</t>
-  </si>
-  <si>
-    <t>B0CJR76Y7G</t>
-  </si>
-  <si>
-    <t>B0G53LZNY3</t>
-  </si>
-  <si>
-    <t>B0BLKB55BM</t>
-  </si>
-  <si>
-    <t>B0FPR962YS</t>
-  </si>
-  <si>
-    <t>B0GKPXQ8G3</t>
-  </si>
-  <si>
-    <t>B0G2C2RCXN</t>
-  </si>
-  <si>
-    <t>B0FJ2LQT7K</t>
-  </si>
-  <si>
-    <t>B0FJ8S5XJ8</t>
-  </si>
-  <si>
-    <t>B0G53PRM34</t>
-  </si>
-  <si>
-    <t>B0FVM17Q4W</t>
-  </si>
-  <si>
-    <t>B0FTVV1QJY</t>
-  </si>
-  <si>
-    <t>B0FJ2J6MTF</t>
-  </si>
-  <si>
-    <t>B0CM9L1QZG</t>
-  </si>
-  <si>
-    <t>B0CF5R3V95</t>
-  </si>
-  <si>
-    <t>B0FN7B3KWS</t>
-  </si>
-  <si>
-    <t>B0FQJWWDVK</t>
-  </si>
-  <si>
-    <t>B0G39ZHDYP</t>
-  </si>
-  <si>
-    <t>B0C4YTNJG7</t>
-  </si>
-  <si>
-    <t>B0CBC7QMNV</t>
-  </si>
-  <si>
-    <t>B0CH4R1V6S</t>
-  </si>
-  <si>
-    <t>B0FTVVLNS9</t>
-  </si>
-  <si>
-    <t>B0FQBX8J17</t>
-  </si>
-  <si>
-    <t>B0FG88HVQ8</t>
-  </si>
-  <si>
-    <t>B0FJ8PZ9H7</t>
-  </si>
-  <si>
-    <t>B0B4KC7VBM</t>
-  </si>
-  <si>
-    <t>B0GXPBHDRF</t>
-  </si>
-  <si>
-    <t>B0DXFPM4N2</t>
-  </si>
-  <si>
-    <t>B0FJ2JJZL3</t>
-  </si>
-  <si>
-    <t>B0CM9HYVDM</t>
-  </si>
-  <si>
-    <t>B0B4G19R58</t>
-  </si>
-  <si>
-    <t>B0GCP1J2HC</t>
-  </si>
-  <si>
-    <t>B0FJ2DT13L</t>
-  </si>
-  <si>
-    <t>B0FQBXS6Y2</t>
-  </si>
-  <si>
-    <t>B0G53KWRVW</t>
-  </si>
-  <si>
-    <t>B0B4G8ZB64</t>
-  </si>
-  <si>
-    <t>B0GN8MFDGZ</t>
-  </si>
-  <si>
-    <t>B0FTVS34SD</t>
-  </si>
-  <si>
-    <t>B0FN7DYB2M</t>
-  </si>
-  <si>
-    <t>B0FQBWV1ST</t>
-  </si>
-  <si>
-    <t>B0BPLZ5CGV</t>
-  </si>
-  <si>
-    <t>B0DN6PFWNK</t>
-  </si>
-  <si>
-    <t>B0DN6MNS1X</t>
-  </si>
-  <si>
-    <t>B0G53H49BS</t>
-  </si>
-  <si>
-    <t>B0CF5SHL15</t>
-  </si>
-  <si>
-    <t>B0D3LZWTHV</t>
-  </si>
-  <si>
-    <t>B0D3Q2T5XX</t>
-  </si>
-  <si>
-    <t>B0BLNCP74M</t>
-  </si>
-  <si>
-    <t>B0FQBTRM28</t>
-  </si>
-  <si>
-    <t>B0B4JRQP22</t>
-  </si>
-  <si>
-    <t>B0C4YT43Z3</t>
-  </si>
-  <si>
-    <t>B0FTVQQVDC</t>
-  </si>
-  <si>
-    <t>B0CM6NVLT9</t>
-  </si>
-  <si>
-    <t>B0B4DPX2J2</t>
-  </si>
-  <si>
-    <t>B0DT6T6N6B</t>
-  </si>
-  <si>
-    <t>B0G3Q59X8C</t>
-  </si>
-  <si>
-    <t>B0B4G763WS</t>
-  </si>
-  <si>
-    <t>B0FTVSH458</t>
-  </si>
-  <si>
-    <t>B0BQ7H7418</t>
-  </si>
-  <si>
-    <t>B0B4G59Y8W</t>
-  </si>
-  <si>
-    <t>B0BLJVJ2GN</t>
-  </si>
-  <si>
-    <t>B0B4G1PXWV</t>
-  </si>
-  <si>
-    <t>B0B4G94VP3</t>
-  </si>
-  <si>
-    <t>B0FN7C25VS</t>
-  </si>
-  <si>
-    <t>B0FLYJFC22</t>
-  </si>
-  <si>
-    <t>B0CX1XK5R6</t>
-  </si>
-  <si>
-    <t>B0CH4RNWJX</t>
-  </si>
-  <si>
-    <t>B0B4G5ZLTB</t>
-  </si>
-  <si>
-    <t>B0FF9R3GKK</t>
-  </si>
-  <si>
-    <t>B0G53KWRWH</t>
-  </si>
-  <si>
-    <t>B0CM9P5CCK</t>
-  </si>
-  <si>
-    <t>B0G53M9258</t>
-  </si>
-  <si>
-    <t>B0G3B152FR</t>
-  </si>
-  <si>
-    <t>B0C4YSV3XL</t>
-  </si>
-  <si>
-    <t>B0GW8R2RYM</t>
-  </si>
-  <si>
-    <t>B0CH4VCD6R</t>
-  </si>
-  <si>
-    <t>B0B4G7VWXD</t>
-  </si>
-  <si>
-    <t>B0B4G89VQJ</t>
-  </si>
-  <si>
-    <t>B0DFMMTWLY</t>
-  </si>
-  <si>
-    <t>B0CKHVHVQ1</t>
-  </si>
-  <si>
-    <t>B0GN8RQJRG</t>
-  </si>
-  <si>
-    <t>B0B4G8PH2P</t>
-  </si>
-  <si>
-    <t>B0GW96CQMG</t>
-  </si>
-  <si>
     <t>Audio Array</t>
   </si>
   <si>
+    <t>AM-C24</t>
+  </si>
+  <si>
+    <t>AM-C7</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>AA-02</t>
+  </si>
+  <si>
+    <t>AM-C31</t>
+  </si>
+  <si>
+    <t>AM-W14</t>
+  </si>
+  <si>
+    <t>AH-45 BK</t>
+  </si>
+  <si>
+    <t>AM-C44 Pro</t>
+  </si>
+  <si>
+    <t>AA-04</t>
+  </si>
+  <si>
+    <t>AK-37-W</t>
+  </si>
+  <si>
+    <t>GB-02 (AM-C43 + AI-11)</t>
+  </si>
+  <si>
+    <t>KB-01 (AM-W32 + AI-12)</t>
+  </si>
+  <si>
+    <t>AM-C42</t>
+  </si>
+  <si>
+    <t>AA-19WL</t>
+  </si>
+  <si>
+    <t>AA-05</t>
+  </si>
+  <si>
+    <t>AM-W23</t>
+  </si>
+  <si>
+    <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+  </si>
+  <si>
+    <t>AM-W15</t>
+  </si>
+  <si>
+    <t>AM-C49</t>
+  </si>
+  <si>
+    <t>AM-Mix10</t>
+  </si>
+  <si>
+    <t>GB-05 (AM-C43 + AI-06)</t>
+  </si>
+  <si>
+    <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+  </si>
+  <si>
+    <t>UB-02 (AM-S1 + AA-21)</t>
+  </si>
+  <si>
+    <t>AM-C6</t>
+  </si>
+  <si>
+    <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+  </si>
+  <si>
+    <t>GB-04 (AM-C45 + AI-06)</t>
+  </si>
+  <si>
+    <t>AM-W46</t>
+  </si>
+  <si>
+    <t>AH-50</t>
+  </si>
+  <si>
+    <t>AM-C52</t>
+  </si>
+  <si>
+    <t>PB-08 (AM-C1 + AI-04)</t>
+  </si>
+  <si>
+    <t>BE-4T</t>
+  </si>
+  <si>
+    <t>AM-Mix6</t>
+  </si>
+  <si>
+    <t>AM-C20</t>
+  </si>
+  <si>
+    <t>AA-01</t>
+  </si>
+  <si>
+    <t>PB-13 (AM-C43+AH-40-SL+AI-11)</t>
+  </si>
+  <si>
+    <t>AM-C11 Pro</t>
+  </si>
+  <si>
+    <t>AH-60-BL</t>
+  </si>
+  <si>
+    <t>AM-W11</t>
+  </si>
+  <si>
+    <t>AM-C19</t>
+  </si>
+  <si>
+    <t>AM-C40</t>
+  </si>
+  <si>
+    <t>AA-25</t>
+  </si>
+  <si>
+    <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+  </si>
+  <si>
+    <t>AC-6XL</t>
+  </si>
+  <si>
+    <t>AA-21</t>
+  </si>
+  <si>
+    <t>AM-W45</t>
+  </si>
+  <si>
+    <t>AI-11</t>
+  </si>
+  <si>
+    <t>AM-W18</t>
+  </si>
+  <si>
+    <t>GB-01 (AM-C43 +AI-10)</t>
+  </si>
+  <si>
+    <t>AK-61 Neo</t>
+  </si>
+  <si>
+    <t>AM-C48</t>
+  </si>
+  <si>
+    <t>SB-01</t>
+  </si>
+  <si>
+    <t>AM-C3a</t>
+  </si>
+  <si>
+    <t>AA-03</t>
+  </si>
+  <si>
+    <t>AA-22</t>
+  </si>
+  <si>
+    <t>AM-W20</t>
+  </si>
+  <si>
+    <t>AM-W13</t>
+  </si>
+  <si>
+    <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+  </si>
+  <si>
+    <t>AM-C39</t>
+  </si>
+  <si>
+    <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+  </si>
+  <si>
+    <t>AI-12</t>
+  </si>
+  <si>
+    <t>AI-14</t>
+  </si>
+  <si>
+    <t>AM-W47 Wireless</t>
+  </si>
+  <si>
+    <t>AM-C43</t>
+  </si>
+  <si>
+    <t>AM-C10</t>
+  </si>
+  <si>
+    <t>AM-W22</t>
+  </si>
+  <si>
+    <t>AM-C25</t>
+  </si>
+  <si>
+    <t>AI-13</t>
+  </si>
+  <si>
+    <t>AM-C1</t>
+  </si>
+  <si>
+    <t>AM-C11X Pro</t>
+  </si>
+  <si>
+    <t>AM-S1</t>
+  </si>
+  <si>
+    <t>AM-W36 Pro</t>
+  </si>
+  <si>
+    <t>MT-12</t>
+  </si>
+  <si>
+    <t>AM-C50</t>
+  </si>
+  <si>
+    <t>AM-W24</t>
+  </si>
+  <si>
+    <t>AM-C51</t>
+  </si>
+  <si>
+    <t>AM-C11X</t>
+  </si>
+  <si>
+    <t>AM-W33</t>
+  </si>
+  <si>
+    <t>AM-W19</t>
+  </si>
+  <si>
+    <t>AC-3XL</t>
+  </si>
+  <si>
+    <t>AM-C45 Pro</t>
+  </si>
+  <si>
+    <t>T-835</t>
+  </si>
+  <si>
+    <t>AM-W21</t>
+  </si>
+  <si>
+    <t>GB-03 (AI-12 + AM-C43)</t>
+  </si>
+  <si>
+    <t>AH-40 SL</t>
+  </si>
+  <si>
+    <t>AA-20</t>
+  </si>
+  <si>
+    <t>AM-C45</t>
+  </si>
+  <si>
+    <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+  </si>
+  <si>
+    <t>AA-06</t>
+  </si>
+  <si>
+    <t>AM-W33 Pro</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>AM-Pro12</t>
+  </si>
+  <si>
+    <t>AM-C41</t>
+  </si>
+  <si>
+    <t>AA-19</t>
+  </si>
+  <si>
+    <t>AM-W47 Wired</t>
+  </si>
+  <si>
+    <t>AH-60-RD</t>
+  </si>
+  <si>
+    <t>AM-C3</t>
+  </si>
+  <si>
+    <t>AI-06</t>
+  </si>
+  <si>
+    <t>AM-C27</t>
+  </si>
+  <si>
+    <t>AM-W34</t>
+  </si>
+  <si>
+    <t>AM-C4</t>
+  </si>
+  <si>
+    <t>AM-C11</t>
+  </si>
+  <si>
+    <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+  </si>
+  <si>
+    <t>AM-C44</t>
+  </si>
+  <si>
+    <t>AM-S2</t>
+  </si>
+  <si>
+    <t>AK-37-B</t>
+  </si>
+  <si>
+    <t>AA-19BL</t>
+  </si>
+  <si>
     <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
   </si>
   <si>
-    <t>AM-C41</t>
+    <t>AM-C2</t>
+  </si>
+  <si>
+    <t>AI-04 Red</t>
+  </si>
+  <si>
+    <t>AM-W10</t>
+  </si>
+  <si>
+    <t>AI-10</t>
+  </si>
+  <si>
+    <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+  </si>
+  <si>
+    <t>AM-W35</t>
+  </si>
+  <si>
+    <t>AM-W17</t>
+  </si>
+  <si>
+    <t>AM-Pro8</t>
+  </si>
+  <si>
+    <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
   </si>
   <si>
     <t>AM-C46</t>
   </si>
   <si>
-    <t>GB-04 (AM-C45 + AI-06)</t>
-  </si>
-  <si>
-    <t>AM-C7</t>
-  </si>
-  <si>
-    <t>AM-C19</t>
-  </si>
-  <si>
-    <t>AM-C24</t>
-  </si>
-  <si>
-    <t>AM-W20</t>
-  </si>
-  <si>
-    <t>AM-C50</t>
+    <t>AM-W16</t>
+  </si>
+  <si>
+    <t>AM-W36</t>
+  </si>
+  <si>
+    <t>PB-01 (AM-C11 + AI-04)</t>
+  </si>
+  <si>
+    <t>AM-C30</t>
+  </si>
+  <si>
+    <t>AA-26</t>
+  </si>
+  <si>
+    <t>AM-C18</t>
+  </si>
+  <si>
+    <t>AI-03</t>
+  </si>
+  <si>
+    <t>AK-61 Pro</t>
+  </si>
+  <si>
+    <t>AM-C5</t>
+  </si>
+  <si>
+    <t>AM-C47</t>
+  </si>
+  <si>
+    <t>BE-4</t>
+  </si>
+  <si>
+    <t>AM-W12</t>
+  </si>
+  <si>
+    <t>AM-C28</t>
+  </si>
+  <si>
+    <t>AM-W32</t>
+  </si>
+  <si>
+    <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
   </si>
   <si>
     <t>UB-03 (AM-S1 + AA-22)</t>
   </si>
   <si>
-    <t>AM-W36</t>
-  </si>
-  <si>
-    <t>AM-C42</t>
-  </si>
-  <si>
-    <t>AM-W33 Pro</t>
-  </si>
-  <si>
-    <t>AM-W32</t>
-  </si>
-  <si>
-    <t>AI-12</t>
-  </si>
-  <si>
-    <t>AM-C20</t>
-  </si>
-  <si>
-    <t>MT-12</t>
-  </si>
-  <si>
-    <t>AM-W21</t>
-  </si>
-  <si>
-    <t>AM-W36 Pro</t>
-  </si>
-  <si>
-    <t>AM-C4</t>
-  </si>
-  <si>
-    <t>AM-W14</t>
-  </si>
-  <si>
-    <t>AI-06</t>
-  </si>
-  <si>
-    <t>GB-05 (AM-C43 + AI-06)</t>
-  </si>
-  <si>
-    <t>SB-01</t>
-  </si>
-  <si>
-    <t>AM-W19</t>
-  </si>
-  <si>
-    <t>AM-W23</t>
-  </si>
-  <si>
-    <t>AM-Pro8</t>
-  </si>
-  <si>
-    <t>AM-C10</t>
-  </si>
-  <si>
-    <t>AK-61 Pro</t>
-  </si>
-  <si>
-    <t>AA-21</t>
-  </si>
-  <si>
-    <t>AA-19BL</t>
-  </si>
-  <si>
-    <t>AM-C48</t>
-  </si>
-  <si>
-    <t>AK-37-W</t>
-  </si>
-  <si>
-    <t>AM-C45 Pro</t>
-  </si>
-  <si>
-    <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
-  </si>
-  <si>
-    <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
-  </si>
-  <si>
-    <t>AM-C39</t>
-  </si>
-  <si>
-    <t>AM-W35</t>
-  </si>
-  <si>
-    <t>AM-C40</t>
-  </si>
-  <si>
-    <t>PB-01 (AM-C11 + AI-04)</t>
-  </si>
-  <si>
     <t>AM-W32 Pro</t>
   </si>
   <si>
-    <t>BE-4</t>
-  </si>
-  <si>
-    <t>AM-C27</t>
-  </si>
-  <si>
-    <t>AM-W34</t>
-  </si>
-  <si>
-    <t>AM-C49</t>
-  </si>
-  <si>
-    <t>AI-10</t>
-  </si>
-  <si>
-    <t>GB-03 (AI-12 + AM-C43)</t>
-  </si>
-  <si>
-    <t>AI-03</t>
-  </si>
-  <si>
-    <t>GB-01 (AM-C43 +AI-10)</t>
-  </si>
-  <si>
-    <t>AM-C52</t>
-  </si>
-  <si>
-    <t>AM-C28</t>
-  </si>
-  <si>
-    <t>AA-20</t>
-  </si>
-  <si>
-    <t>AM-C44</t>
-  </si>
-  <si>
-    <t>AM-S2</t>
-  </si>
-  <si>
-    <t>AM-C11</t>
-  </si>
-  <si>
-    <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
-  </si>
-  <si>
-    <t>AA-25</t>
-  </si>
-  <si>
-    <t>BE-4T</t>
-  </si>
-  <si>
-    <t>AM-C18</t>
-  </si>
-  <si>
-    <t>AM-W22</t>
-  </si>
-  <si>
-    <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
-  </si>
-  <si>
-    <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
-  </si>
-  <si>
-    <t>AM-Mix6</t>
-  </si>
-  <si>
-    <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
-  </si>
-  <si>
-    <t>KB-01 (AM-W32 + AI-12)</t>
-  </si>
-  <si>
-    <t>AM-W16</t>
-  </si>
-  <si>
-    <t>AA-19</t>
-  </si>
-  <si>
-    <t>UB-02 (AM-S1 + AA-21)</t>
-  </si>
-  <si>
-    <t>AC-3XL</t>
-  </si>
-  <si>
-    <t>AM-W47 Wired</t>
-  </si>
-  <si>
-    <t>AM-C30</t>
-  </si>
-  <si>
-    <t>AM-C11X</t>
-  </si>
-  <si>
-    <t>AM-C3a</t>
-  </si>
-  <si>
-    <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
-  </si>
-  <si>
-    <t>AH-40 SL</t>
-  </si>
-  <si>
-    <t>AH-50</t>
-  </si>
-  <si>
-    <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
-  </si>
-  <si>
-    <t>AM-C5</t>
-  </si>
-  <si>
-    <t>M6</t>
-  </si>
-  <si>
-    <t>AM-S1</t>
-  </si>
-  <si>
-    <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
-  </si>
-  <si>
-    <t>AM-W18</t>
-  </si>
-  <si>
-    <t>AM-C2</t>
-  </si>
-  <si>
-    <t>M8</t>
-  </si>
-  <si>
-    <t>GB-02 (AM-C43 + AI-11)</t>
-  </si>
-  <si>
-    <t>AH-45 BK</t>
-  </si>
-  <si>
-    <t>AM-Mix10</t>
-  </si>
-  <si>
-    <t>AM-C3</t>
-  </si>
-  <si>
-    <t>AK-61 Neo</t>
-  </si>
-  <si>
-    <t>PB-13 (AM-C43+AH-40-SL+AI-11)</t>
-  </si>
-  <si>
-    <t>PB-08 (AM-C1 + AI-04)</t>
-  </si>
-  <si>
-    <t>AH-60-RD</t>
-  </si>
-  <si>
-    <t>AI-04 Red</t>
-  </si>
-  <si>
-    <t>AM-C44 Pro</t>
-  </si>
-  <si>
-    <t>AM-C11 Pro</t>
-  </si>
-  <si>
-    <t>AI-13</t>
-  </si>
-  <si>
-    <t>AA-22</t>
-  </si>
-  <si>
-    <t>AM-C45</t>
-  </si>
-  <si>
-    <t>AA-19WL</t>
-  </si>
-  <si>
-    <t>AM-C25</t>
-  </si>
-  <si>
-    <t>AH-60-BL</t>
-  </si>
-  <si>
-    <t>AA-02</t>
-  </si>
-  <si>
-    <t>AM-C31</t>
-  </si>
-  <si>
-    <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
-  </si>
-  <si>
-    <t>AI-11</t>
-  </si>
-  <si>
-    <t>AM-C1</t>
-  </si>
-  <si>
-    <t>AA-26</t>
-  </si>
-  <si>
-    <t>AM-W24</t>
-  </si>
-  <si>
-    <t>AM-W12</t>
-  </si>
-  <si>
-    <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
-  </si>
-  <si>
-    <t>AA-06</t>
-  </si>
-  <si>
-    <t>AM-W13</t>
-  </si>
-  <si>
-    <t>AA-05</t>
-  </si>
-  <si>
-    <t>AM-C6</t>
-  </si>
-  <si>
-    <t>AA-03</t>
-  </si>
-  <si>
-    <t>AM-C11X Pro</t>
-  </si>
-  <si>
-    <t>AM-W46</t>
-  </si>
-  <si>
-    <t>AM-C43</t>
-  </si>
-  <si>
-    <t>AM-W11</t>
-  </si>
-  <si>
-    <t>AM-C47</t>
-  </si>
-  <si>
-    <t>AM-Pro12</t>
-  </si>
-  <si>
-    <t>AM-W17</t>
-  </si>
-  <si>
-    <t>AI-14</t>
-  </si>
-  <si>
-    <t>AM-W47 Wireless</t>
-  </si>
-  <si>
-    <t>AM-W15</t>
-  </si>
-  <si>
-    <t>AM-C51</t>
-  </si>
-  <si>
-    <t>AC-6XL</t>
-  </si>
-  <si>
-    <t>AA-04</t>
-  </si>
-  <si>
-    <t>AM-W10</t>
-  </si>
-  <si>
-    <t>AM-W33</t>
-  </si>
-  <si>
-    <t>AM-W45</t>
-  </si>
-  <si>
-    <t>AK-37-B</t>
-  </si>
-  <si>
-    <t>AA-01</t>
-  </si>
-  <si>
-    <t>T-835</t>
+    <t>Microphone Condenser</t>
+  </si>
+  <si>
+    <t>Audio Mixer</t>
+  </si>
+  <si>
+    <t>Microphone Accessories</t>
+  </si>
+  <si>
+    <t>Microphone Wireless Handheld</t>
+  </si>
+  <si>
+    <t>DJ Headphone</t>
+  </si>
+  <si>
+    <t>Microphone Dynamic</t>
+  </si>
+  <si>
+    <t>Electric Keyboard</t>
   </si>
   <si>
     <t>Bundles</t>
   </si>
   <si>
-    <t>Microphone Condenser</t>
-  </si>
-  <si>
     <t>Microphone Wireless Lapel</t>
   </si>
   <si>
-    <t>Microphone Dynamic</t>
-  </si>
-  <si>
-    <t>Microphone Wireless Handheld</t>
+    <t>Speaker Karaoke</t>
+  </si>
+  <si>
+    <t>Headphone</t>
+  </si>
+  <si>
+    <t>Monitor Speakers Accessories</t>
+  </si>
+  <si>
+    <t>Microphone Conference</t>
   </si>
   <si>
     <t>Audio Interface</t>
   </si>
   <si>
-    <t>Audio Mixer</t>
-  </si>
-  <si>
     <t>Sound Bar</t>
   </si>
   <si>
-    <t>Microphone Conference</t>
-  </si>
-  <si>
-    <t>Electric Keyboard</t>
-  </si>
-  <si>
-    <t>Monitor Speakers Accessories</t>
-  </si>
-  <si>
-    <t>Microphone Accessories</t>
+    <t>Voice Amplifier</t>
   </si>
   <si>
     <t>Monitor Speakers</t>
@@ -1354,205 +1366,193 @@
     <t>Microphone dynamic</t>
   </si>
   <si>
-    <t>Voice Amplifier</t>
-  </si>
-  <si>
-    <t>DJ Headphone</t>
-  </si>
-  <si>
-    <t>Speaker Karaoke</t>
-  </si>
-  <si>
-    <t>Headphone</t>
+    <t>USB Microphone Kit - Tripod</t>
+  </si>
+  <si>
+    <t>USB Microphone Kit - Boomarm</t>
+  </si>
+  <si>
+    <t>8 channels Mixer</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Wireless Microphone</t>
+  </si>
+  <si>
+    <t>37 Key Electronic Keyboard White</t>
+  </si>
+  <si>
+    <t>GB-02</t>
+  </si>
+  <si>
+    <t>KB-01</t>
+  </si>
+  <si>
+    <t>Wireless Lapel Microphone</t>
+  </si>
+  <si>
+    <t>PB-12</t>
+  </si>
+  <si>
+    <t>Wireless Mic with Charging Case</t>
+  </si>
+  <si>
+    <t>Vocal Microphone</t>
+  </si>
+  <si>
+    <t>10 channels mixer</t>
+  </si>
+  <si>
+    <t>GB-05</t>
+  </si>
+  <si>
+    <t>PB-10</t>
+  </si>
+  <si>
+    <t>UB-02</t>
+  </si>
+  <si>
+    <t>PB-14</t>
+  </si>
+  <si>
+    <t>GB-04</t>
+  </si>
+  <si>
+    <t>Microphone with Speaker</t>
+  </si>
+  <si>
+    <t>PB-08</t>
+  </si>
+  <si>
+    <t>4 channels mixer with OTG</t>
+  </si>
+  <si>
+    <t>6 channels mixer</t>
+  </si>
+  <si>
+    <t>PB-13</t>
+  </si>
+  <si>
+    <t>Condenser Mic with Boom Arm</t>
+  </si>
+  <si>
+    <t>PB-02</t>
+  </si>
+  <si>
+    <t>Monitor Speaker Stand Pair</t>
+  </si>
+  <si>
+    <t>Wireless Conference Microphone</t>
+  </si>
+  <si>
+    <t>GB-01</t>
+  </si>
+  <si>
+    <t>61 Key Electronic Keyboard With LED DIsplay</t>
+  </si>
+  <si>
+    <t>UB-01</t>
+  </si>
+  <si>
+    <t>XLR Microphone Kit - Tripod</t>
+  </si>
+  <si>
+    <t>PB-03</t>
+  </si>
+  <si>
+    <t>Wireless Voice Amplifier</t>
+  </si>
+  <si>
+    <t>XLR Microphone Kit - Boomarm</t>
+  </si>
+  <si>
+    <t>Conference Microphone</t>
+  </si>
+  <si>
+    <t>4 channels Mixer</t>
+  </si>
+  <si>
+    <t>Studio Monitor Speaker</t>
+  </si>
+  <si>
+    <t>Dual UHF Wireless Microphone With Receiver Box</t>
+  </si>
+  <si>
+    <t>12 channels Mixer</t>
+  </si>
+  <si>
+    <t>XLR Dynamic Mic</t>
+  </si>
+  <si>
+    <t>Quad UHF Wireless Microphone With Receiver Box</t>
+  </si>
+  <si>
+    <t>GB-03</t>
+  </si>
+  <si>
+    <t>Dynamic Microphone</t>
+  </si>
+  <si>
+    <t>PB-07</t>
+  </si>
+  <si>
+    <t>Single UHF Wireless Microphone With Receiver</t>
+  </si>
+  <si>
+    <t>06 channels Mixer</t>
+  </si>
+  <si>
+    <t>Wired Voice Amplifier</t>
+  </si>
+  <si>
+    <t>USB/XLR Dynamic Mic</t>
+  </si>
+  <si>
+    <t>PB-06</t>
+  </si>
+  <si>
+    <t>37 Key Electronic Keyboard Black</t>
   </si>
   <si>
     <t>PB-05</t>
   </si>
   <si>
-    <t>USB Microphone Kit - Tripod</t>
-  </si>
-  <si>
-    <t>Condenser Mic with Boom Arm</t>
-  </si>
-  <si>
-    <t>GB-04</t>
-  </si>
-  <si>
-    <t>USB Microphone Kit - Boomarm</t>
-  </si>
-  <si>
-    <t>Wireless Lapel Microphone</t>
-  </si>
-  <si>
-    <t>Vocal Microphone</t>
+    <t>PB-11</t>
+  </si>
+  <si>
+    <t>PB-09</t>
+  </si>
+  <si>
+    <t>PB-01</t>
+  </si>
+  <si>
+    <t>RGB USB Microphone Kit - Tripod</t>
+  </si>
+  <si>
+    <t>Mobile Microphone</t>
+  </si>
+  <si>
+    <t>61 Key Electronic Keyboard With LCD DIsplay</t>
+  </si>
+  <si>
+    <t>04 channels Mixer</t>
+  </si>
+  <si>
+    <t>PB-04</t>
   </si>
   <si>
     <t>UB-03</t>
   </si>
   <si>
-    <t>Wireless Microphone</t>
-  </si>
-  <si>
-    <t>Single UHF Wireless Microphone With Receiver</t>
-  </si>
-  <si>
-    <t>12 channels Mixer</t>
-  </si>
-  <si>
-    <t>Dual UHF Wireless Microphone With Receiver Box</t>
-  </si>
-  <si>
-    <t>GB-05</t>
-  </si>
-  <si>
-    <t>8 channels Mixer</t>
-  </si>
-  <si>
-    <t>Conference Microphone</t>
-  </si>
-  <si>
-    <t>61 Key Electronic Keyboard With LCD DIsplay</t>
-  </si>
-  <si>
-    <t>Monitor Speaker Stand Pair</t>
-  </si>
-  <si>
-    <t>Accessories</t>
-  </si>
-  <si>
-    <t>37 Key Electronic Keyboard White</t>
-  </si>
-  <si>
-    <t>PB-09</t>
-  </si>
-  <si>
-    <t>PB-06</t>
-  </si>
-  <si>
-    <t>XLR Microphone Kit - Tripod</t>
-  </si>
-  <si>
-    <t>PB-01</t>
-  </si>
-  <si>
     <t>Dual UHF Wireless Microphone With Receiver</t>
   </si>
   <si>
-    <t>04 channels Mixer</t>
-  </si>
-  <si>
-    <t>GB-03</t>
-  </si>
-  <si>
-    <t>GB-01</t>
-  </si>
-  <si>
-    <t>Dynamic Microphone</t>
-  </si>
-  <si>
-    <t>Studio Monitor Speaker</t>
-  </si>
-  <si>
-    <t>USB/XLR Dynamic Mic</t>
-  </si>
-  <si>
-    <t>PB-07</t>
-  </si>
-  <si>
-    <t>4 channels mixer with OTG</t>
-  </si>
-  <si>
-    <t>Mobile Microphone</t>
-  </si>
-  <si>
-    <t>PB-02</t>
-  </si>
-  <si>
-    <t>PB-03</t>
-  </si>
-  <si>
-    <t>6 channels mixer</t>
-  </si>
-  <si>
-    <t>PB-14</t>
-  </si>
-  <si>
-    <t>KB-01</t>
-  </si>
-  <si>
-    <t>UB-02</t>
-  </si>
-  <si>
-    <t>Wired Voice Amplifier</t>
-  </si>
-  <si>
-    <t>RGB USB Microphone Kit - Tripod</t>
-  </si>
-  <si>
-    <t>XLR Dynamic Mic</t>
-  </si>
-  <si>
-    <t>PB-12</t>
-  </si>
-  <si>
-    <t>PB-04</t>
-  </si>
-  <si>
-    <t>06 channels Mixer</t>
-  </si>
-  <si>
-    <t>UB-01</t>
-  </si>
-  <si>
-    <t>Microphone with Speaker</t>
-  </si>
-  <si>
-    <t>XLR Microphone Kit - Boomarm</t>
-  </si>
-  <si>
-    <t>GB-02</t>
-  </si>
-  <si>
-    <t>10 channels mixer</t>
-  </si>
-  <si>
-    <t>61 Key Electronic Keyboard With LED DIsplay</t>
-  </si>
-  <si>
-    <t>PB-13</t>
-  </si>
-  <si>
-    <t>PB-08</t>
-  </si>
-  <si>
-    <t>4 channels Mixer</t>
-  </si>
-  <si>
-    <t>PB-10</t>
-  </si>
-  <si>
-    <t>PB-11</t>
-  </si>
-  <si>
-    <t>Wireless Voice Amplifier</t>
-  </si>
-  <si>
-    <t>Wireless Mic with Charging Case</t>
-  </si>
-  <si>
-    <t>Wireless Conference Microphone</t>
-  </si>
-  <si>
-    <t>37 Key Electronic Keyboard Black</t>
-  </si>
-  <si>
-    <t>Quad UHF Wireless Microphone With Receiver Box</t>
-  </si>
-  <si>
     <t>1p</t>
   </si>
   <si>
-    <t>2026-08-14</t>
+    <t>2026-08-15</t>
   </si>
 </sst>
 </file>
@@ -1986,10 +1986,10 @@
         <v>450</v>
       </c>
       <c r="H2">
-        <v>5118.2854</v>
+        <v>1676.644024574118</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J2" t="s">
         <v>511</v>
@@ -1998,16 +1998,16 @@
         <v>33</v>
       </c>
       <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
         <v>1</v>
       </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="O2">
-        <v>3</v>
-      </c>
       <c r="P2">
-        <v>102773.72</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="s">
         <v>512</v>
@@ -2027,16 +2027,16 @@
         <v>299</v>
       </c>
       <c r="E3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F3" t="s">
         <v>451</v>
       </c>
       <c r="H3">
-        <v>1043.232336</v>
+        <v>2051.276637829411</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J3" t="s">
         <v>511</v>
@@ -2045,16 +2045,16 @@
         <v>33</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>14949.82</v>
+        <v>2050.99</v>
       </c>
       <c r="Q3" t="s">
         <v>512</v>
@@ -2071,19 +2071,19 @@
         <v>297</v>
       </c>
       <c r="D4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E4" t="s">
         <v>433</v>
       </c>
       <c r="F4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H4">
-        <v>1043.232336</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I4">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="J4" t="s">
         <v>511</v>
@@ -2092,16 +2092,16 @@
         <v>33</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="N4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>48613.87</v>
+        <v>509663.66</v>
       </c>
       <c r="Q4" t="s">
         <v>512</v>
@@ -2118,19 +2118,19 @@
         <v>297</v>
       </c>
       <c r="D5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H5">
-        <v>2021.262651</v>
+        <v>1330.281037275</v>
       </c>
       <c r="I5">
-        <v>257</v>
+        <v>142</v>
       </c>
       <c r="J5" t="s">
         <v>511</v>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>683148.96</v>
+        <v>240612.54</v>
       </c>
       <c r="Q5" t="s">
         <v>512</v>
@@ -2165,19 +2165,19 @@
         <v>297</v>
       </c>
       <c r="D6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E6" t="s">
         <v>432</v>
       </c>
       <c r="F6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H6">
-        <v>4630.8156</v>
+        <v>3835.413</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J6" t="s">
         <v>511</v>
@@ -2189,13 +2189,10 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
-      </c>
-      <c r="P6">
-        <v>41946.83</v>
       </c>
       <c r="Q6" t="s">
         <v>512</v>
@@ -2212,19 +2209,19 @@
         <v>297</v>
       </c>
       <c r="D7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F7" t="s">
         <v>454</v>
       </c>
       <c r="H7">
-        <v>2051.276637829411</v>
+        <v>3221.74692</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="J7" t="s">
         <v>511</v>
@@ -2233,16 +2230,16 @@
         <v>33</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>2050.99</v>
+        <v>247971.79</v>
       </c>
       <c r="Q7" t="s">
         <v>512</v>
@@ -2259,19 +2256,19 @@
         <v>297</v>
       </c>
       <c r="D8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F8" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="H8">
-        <v>1642.572937873306</v>
+        <v>614.5220519999999</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="J8" t="s">
         <v>511</v>
@@ -2280,13 +2277,16 @@
         <v>33</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N8">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="P8">
+        <v>313904.84</v>
       </c>
       <c r="Q8" t="s">
         <v>512</v>
@@ -2303,19 +2303,19 @@
         <v>297</v>
       </c>
       <c r="D9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E9" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F9" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="H9">
-        <v>1676.644024574118</v>
+        <v>3277.450944</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J9" t="s">
         <v>511</v>
@@ -2327,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>81023.5</v>
       </c>
       <c r="Q9" t="s">
         <v>512</v>
@@ -2350,19 +2350,19 @@
         <v>297</v>
       </c>
       <c r="D10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E10" t="s">
         <v>434</v>
       </c>
       <c r="F10" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H10">
-        <v>2164.7070972</v>
+        <v>871.9473036705882</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="J10" t="s">
         <v>511</v>
@@ -2371,16 +2371,16 @@
         <v>33</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P10">
-        <v>12578.82</v>
+        <v>64678.32</v>
       </c>
       <c r="Q10" t="s">
         <v>512</v>
@@ -2397,19 +2397,19 @@
         <v>297</v>
       </c>
       <c r="D11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E11" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H11">
-        <v>534.6565721999999</v>
+        <v>2335.8554064</v>
       </c>
       <c r="I11">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J11" t="s">
         <v>511</v>
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>34079.43</v>
+        <v>81159.23</v>
       </c>
       <c r="Q11" t="s">
         <v>512</v>
@@ -2444,19 +2444,19 @@
         <v>297</v>
       </c>
       <c r="D12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E12" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H12">
-        <v>5619.632</v>
+        <v>1983.58</v>
       </c>
       <c r="I12">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s">
         <v>511</v>
@@ -2465,16 +2465,16 @@
         <v>33</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>147521.59</v>
+        <v>57112.05</v>
       </c>
       <c r="Q12" t="s">
         <v>512</v>
@@ -2491,19 +2491,19 @@
         <v>297</v>
       </c>
       <c r="D13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E13" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H13">
-        <v>4042.525302</v>
+        <v>2630.5268</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
         <v>511</v>
@@ -2512,16 +2512,16 @@
         <v>33</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>22371.17</v>
+        <v>83470.71000000001</v>
       </c>
       <c r="Q13" t="s">
         <v>512</v>
@@ -2538,13 +2538,13 @@
         <v>297</v>
       </c>
       <c r="D14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F14" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="H14">
         <v>1499.646483</v>
@@ -2585,19 +2585,19 @@
         <v>297</v>
       </c>
       <c r="D15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E15" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F15" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="H15">
-        <v>1825.656588</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
         <v>511</v>
@@ -2606,16 +2606,16 @@
         <v>33</v>
       </c>
       <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>6</v>
+      </c>
+      <c r="O15">
         <v>3</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
       <c r="P15">
-        <v>40263.18</v>
+        <v>58874.55</v>
       </c>
       <c r="Q15" t="s">
         <v>512</v>
@@ -2632,19 +2632,19 @@
         <v>297</v>
       </c>
       <c r="D16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E16" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F16" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="H16">
-        <v>2167.31517804</v>
+        <v>280.0829144294117</v>
       </c>
       <c r="I16">
-        <v>34</v>
+        <v>464</v>
       </c>
       <c r="J16" t="s">
         <v>511</v>
@@ -2653,16 +2653,16 @@
         <v>33</v>
       </c>
       <c r="M16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P16">
-        <v>97369</v>
+        <v>216487.02</v>
       </c>
       <c r="Q16" t="s">
         <v>512</v>
@@ -2679,19 +2679,19 @@
         <v>297</v>
       </c>
       <c r="D17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E17" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F17" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="H17">
-        <v>678.1010183999999</v>
+        <v>1566.15254442</v>
       </c>
       <c r="I17">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="J17" t="s">
         <v>511</v>
@@ -2700,16 +2700,16 @@
         <v>33</v>
       </c>
       <c r="M17">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="O17">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P17">
-        <v>68048.91</v>
+        <v>115520.75</v>
       </c>
       <c r="Q17" t="s">
         <v>512</v>
@@ -2726,19 +2726,19 @@
         <v>297</v>
       </c>
       <c r="D18" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E18" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F18" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="H18">
-        <v>1235.473403164659</v>
+        <v>6152.0362</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
         <v>511</v>
@@ -2750,13 +2750,13 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>3729.48</v>
+        <v>184995.63</v>
       </c>
       <c r="Q18" t="s">
         <v>512</v>
@@ -2773,19 +2773,19 @@
         <v>297</v>
       </c>
       <c r="D19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E19" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F19" t="s">
         <v>460</v>
       </c>
       <c r="H19">
-        <v>4119.760313999999</v>
+        <v>11761.9332</v>
       </c>
       <c r="I19">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J19" t="s">
         <v>511</v>
@@ -2794,16 +2794,16 @@
         <v>33</v>
       </c>
       <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>1</v>
       </c>
-      <c r="N19">
-        <v>3</v>
-      </c>
       <c r="O19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P19">
-        <v>74737.64999999999</v>
+        <v>11268.54</v>
       </c>
       <c r="Q19" t="s">
         <v>512</v>
@@ -2820,19 +2820,19 @@
         <v>297</v>
       </c>
       <c r="D20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E20" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F20" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="H20">
-        <v>2803.686903</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" t="s">
         <v>511</v>
@@ -2841,7 +2841,7 @@
         <v>33</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>14763.09</v>
+        <v>5818.44</v>
       </c>
       <c r="Q20" t="s">
         <v>512</v>
@@ -2867,19 +2867,19 @@
         <v>297</v>
       </c>
       <c r="D21" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E21" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F21" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H21">
-        <v>4694.545512</v>
+        <v>5808.86204274</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J21" t="s">
         <v>511</v>
@@ -2888,16 +2888,16 @@
         <v>33</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>59425.69</v>
+        <v>159406.06</v>
       </c>
       <c r="Q21" t="s">
         <v>512</v>
@@ -2914,19 +2914,19 @@
         <v>297</v>
       </c>
       <c r="D22" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E22" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F22" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="H22">
-        <v>1700.734990628047</v>
+        <v>3909.104</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J22" t="s">
         <v>511</v>
@@ -2935,16 +2935,16 @@
         <v>33</v>
       </c>
       <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>15</v>
+      </c>
+      <c r="O22">
         <v>1</v>
       </c>
-      <c r="N22">
-        <v>3</v>
-      </c>
-      <c r="O22">
-        <v>2</v>
-      </c>
       <c r="P22">
-        <v>7893.34</v>
+        <v>66064.62</v>
       </c>
       <c r="Q22" t="s">
         <v>512</v>
@@ -2961,19 +2961,19 @@
         <v>297</v>
       </c>
       <c r="D23" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E23" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F23" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="H23">
-        <v>3221.74692</v>
+        <v>4986.467599999999</v>
       </c>
       <c r="I23">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="J23" t="s">
         <v>511</v>
@@ -2982,16 +2982,16 @@
         <v>33</v>
       </c>
       <c r="M23">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P23">
-        <v>252655.78</v>
+        <v>679429.59</v>
       </c>
       <c r="Q23" t="s">
         <v>512</v>
@@ -3008,19 +3008,19 @@
         <v>297</v>
       </c>
       <c r="D24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E24" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F24" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="H24">
-        <v>2934.090945</v>
+        <v>5836.846399999999</v>
       </c>
       <c r="I24">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s">
         <v>511</v>
@@ -3029,16 +3029,16 @@
         <v>33</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>28257.82</v>
+        <v>205552.34</v>
       </c>
       <c r="Q24" t="s">
         <v>512</v>
@@ -3055,19 +3055,19 @@
         <v>297</v>
       </c>
       <c r="D25" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E25" t="s">
         <v>432</v>
       </c>
       <c r="F25" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="H25">
-        <v>3909.104</v>
+        <v>1815.59502123</v>
       </c>
       <c r="I25">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J25" t="s">
         <v>511</v>
@@ -3079,13 +3079,13 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>66064.62</v>
+        <v>11049.23</v>
       </c>
       <c r="Q25" t="s">
         <v>512</v>
@@ -3102,19 +3102,19 @@
         <v>297</v>
       </c>
       <c r="D26" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E26" t="s">
         <v>439</v>
       </c>
       <c r="F26" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="H26">
-        <v>708</v>
+        <v>2280.5034</v>
       </c>
       <c r="I26">
-        <v>271</v>
+        <v>11</v>
       </c>
       <c r="J26" t="s">
         <v>511</v>
@@ -3123,16 +3123,16 @@
         <v>33</v>
       </c>
       <c r="M26">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
       <c r="O26">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="P26">
-        <v>259939.34</v>
+        <v>44601.81</v>
       </c>
       <c r="Q26" t="s">
         <v>512</v>
@@ -3149,19 +3149,19 @@
         <v>297</v>
       </c>
       <c r="D27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E27" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F27" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="H27">
-        <v>1159.29193338</v>
+        <v>4630.8156</v>
       </c>
       <c r="I27">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J27" t="s">
         <v>511</v>
@@ -3170,16 +3170,16 @@
         <v>33</v>
       </c>
       <c r="M27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>74082.34</v>
+        <v>41946.83</v>
       </c>
       <c r="Q27" t="s">
         <v>512</v>
@@ -3196,19 +3196,19 @@
         <v>297</v>
       </c>
       <c r="D28" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E28" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F28" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="H28">
-        <v>1566.15254442</v>
+        <v>4277.252577599999</v>
       </c>
       <c r="I28">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="J28" t="s">
         <v>511</v>
@@ -3220,13 +3220,13 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>115520.75</v>
+        <v>14645.6</v>
       </c>
       <c r="Q28" t="s">
         <v>512</v>
@@ -3243,19 +3243,19 @@
         <v>297</v>
       </c>
       <c r="D29" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E29" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F29" t="s">
-        <v>463</v>
+        <v>436</v>
       </c>
       <c r="H29">
-        <v>12112.09532316</v>
+        <v>1201.7320128</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>642</v>
       </c>
       <c r="J29" t="s">
         <v>511</v>
@@ -3264,16 +3264,16 @@
         <v>33</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="P29">
-        <v>15731.47</v>
+        <v>951217.4</v>
       </c>
       <c r="Q29" t="s">
         <v>512</v>
@@ -3290,19 +3290,19 @@
         <v>297</v>
       </c>
       <c r="D30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E30" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F30" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="H30">
-        <v>2311.522194589411</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I30">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J30" t="s">
         <v>511</v>
@@ -3311,16 +3311,16 @@
         <v>33</v>
       </c>
       <c r="M30">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>1</v>
       </c>
       <c r="P30">
-        <v>72560.19</v>
+        <v>28653.82</v>
       </c>
       <c r="Q30" t="s">
         <v>512</v>
@@ -3337,16 +3337,16 @@
         <v>297</v>
       </c>
       <c r="D31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E31" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F31" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="H31">
-        <v>3317.4116676</v>
+        <v>3358.8228</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P31">
-        <v>3844.94</v>
+        <v>5033.59</v>
       </c>
       <c r="Q31" t="s">
         <v>512</v>
@@ -3384,19 +3384,19 @@
         <v>297</v>
       </c>
       <c r="D32" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E32" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F32" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H32">
-        <v>1722.835557825</v>
+        <v>3040.14077289</v>
       </c>
       <c r="I32">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="J32" t="s">
         <v>511</v>
@@ -3405,16 +3405,16 @@
         <v>33</v>
       </c>
       <c r="M32">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>405793.87</v>
+        <v>243352.92</v>
       </c>
       <c r="Q32" t="s">
         <v>512</v>
@@ -3431,19 +3431,19 @@
         <v>297</v>
       </c>
       <c r="D33" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E33" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="F33" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H33">
-        <v>2973.2121576</v>
+        <v>4696.526757959999</v>
       </c>
       <c r="I33">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="J33" t="s">
         <v>511</v>
@@ -3452,16 +3452,16 @@
         <v>33</v>
       </c>
       <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
         <v>3</v>
       </c>
-      <c r="N33">
-        <v>5</v>
-      </c>
       <c r="O33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>124765.36</v>
+        <v>66417.75</v>
       </c>
       <c r="Q33" t="s">
         <v>512</v>
@@ -3478,19 +3478,19 @@
         <v>297</v>
       </c>
       <c r="D34" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E34" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F34" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="H34">
-        <v>1956.06063</v>
+        <v>1235.473403164659</v>
       </c>
       <c r="I34">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="J34" t="s">
         <v>511</v>
@@ -3499,16 +3499,16 @@
         <v>33</v>
       </c>
       <c r="M34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O34">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P34">
-        <v>181046.2</v>
+        <v>3729.48</v>
       </c>
       <c r="Q34" t="s">
         <v>512</v>
@@ -3525,19 +3525,19 @@
         <v>297</v>
       </c>
       <c r="D35" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E35" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="F35" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="H35">
-        <v>2335.8554064</v>
+        <v>1224.499030661912</v>
       </c>
       <c r="I35">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J35" t="s">
         <v>511</v>
@@ -3549,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35">
-        <v>86961.25999999999</v>
+        <v>32289.31</v>
       </c>
       <c r="Q35" t="s">
         <v>512</v>
@@ -3572,19 +3572,19 @@
         <v>297</v>
       </c>
       <c r="D36" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E36" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F36" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="H36">
-        <v>2458.088208</v>
+        <v>2436.8652</v>
       </c>
       <c r="I36">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="J36" t="s">
         <v>511</v>
@@ -3593,16 +3593,16 @@
         <v>33</v>
       </c>
       <c r="M36">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>21530.69</v>
+        <v>111364.9</v>
       </c>
       <c r="Q36" t="s">
         <v>512</v>
@@ -3619,19 +3619,19 @@
         <v>297</v>
       </c>
       <c r="D37" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E37" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="F37" t="s">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="H37">
-        <v>4889.153</v>
+        <v>3140.890488</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="J37" t="s">
         <v>511</v>
@@ -3643,13 +3643,13 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>39150.73</v>
+        <v>245376.18</v>
       </c>
       <c r="Q37" t="s">
         <v>512</v>
@@ -3666,19 +3666,19 @@
         <v>297</v>
       </c>
       <c r="D38" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E38" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="F38" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="H38">
-        <v>4841.8232</v>
+        <v>1092.483648</v>
       </c>
       <c r="I38">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J38" t="s">
         <v>511</v>
@@ -3687,16 +3687,16 @@
         <v>33</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N38">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P38">
-        <v>111163.58</v>
+        <v>60411.87</v>
       </c>
       <c r="Q38" t="s">
         <v>512</v>
@@ -3713,19 +3713,19 @@
         <v>297</v>
       </c>
       <c r="D39" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E39" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="F39" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="H39">
-        <v>734.122339149</v>
+        <v>2857.758705882353</v>
       </c>
       <c r="I39">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J39" t="s">
         <v>511</v>
@@ -3734,16 +3734,16 @@
         <v>33</v>
       </c>
       <c r="M39">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P39">
-        <v>51132.46</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="s">
         <v>512</v>
@@ -3760,19 +3760,19 @@
         <v>297</v>
       </c>
       <c r="D40" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E40" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F40" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="H40">
-        <v>1984.74951924</v>
+        <v>1642.572937873306</v>
       </c>
       <c r="I40">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J40" t="s">
         <v>511</v>
@@ -3781,16 +3781,13 @@
         <v>33</v>
       </c>
       <c r="M40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>2</v>
-      </c>
-      <c r="P40">
-        <v>44048.43</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="s">
         <v>512</v>
@@ -3807,13 +3804,13 @@
         <v>297</v>
       </c>
       <c r="D41" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E41" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F41" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -3854,19 +3851,19 @@
         <v>297</v>
       </c>
       <c r="D42" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E42" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F42" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="H42">
-        <v>4859.948</v>
+        <v>326.010105</v>
       </c>
       <c r="I42">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="J42" t="s">
         <v>511</v>
@@ -3875,16 +3872,16 @@
         <v>33</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P42">
-        <v>82498.16</v>
+        <v>29715.15</v>
       </c>
       <c r="Q42" t="s">
         <v>512</v>
@@ -3901,19 +3898,19 @@
         <v>297</v>
       </c>
       <c r="D43" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E43" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F43" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H43">
-        <v>3129.697008</v>
+        <v>5118.2854</v>
       </c>
       <c r="I43">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J43" t="s">
         <v>511</v>
@@ -3925,13 +3922,13 @@
         <v>0</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>53620.14</v>
+        <v>120811.9</v>
       </c>
       <c r="Q43" t="s">
         <v>512</v>
@@ -3948,19 +3945,19 @@
         <v>297</v>
       </c>
       <c r="D44" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E44" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F44" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="H44">
-        <v>1948.404289679999</v>
+        <v>169.5252546</v>
       </c>
       <c r="I44">
-        <v>16</v>
+        <v>229</v>
       </c>
       <c r="J44" t="s">
         <v>511</v>
@@ -3969,16 +3966,16 @@
         <v>33</v>
       </c>
       <c r="M44">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O44">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P44">
-        <v>50331.82</v>
+        <v>94390.50999999999</v>
       </c>
       <c r="Q44" t="s">
         <v>512</v>
@@ -3995,19 +3992,19 @@
         <v>297</v>
       </c>
       <c r="D45" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E45" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F45" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="H45">
-        <v>827.5708984229998</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I45">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="J45" t="s">
         <v>511</v>
@@ -4016,16 +4013,16 @@
         <v>33</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="P45">
-        <v>2014.34</v>
+        <v>426256.52</v>
       </c>
       <c r="Q45" t="s">
         <v>512</v>
@@ -4042,19 +4039,19 @@
         <v>297</v>
       </c>
       <c r="D46" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E46" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="F46" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="H46">
-        <v>2360.3131602</v>
+        <v>2738.484882</v>
       </c>
       <c r="I46">
-        <v>12</v>
+        <v>328</v>
       </c>
       <c r="J46" t="s">
         <v>511</v>
@@ -4063,16 +4060,16 @@
         <v>33</v>
       </c>
       <c r="M46">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="N46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P46">
-        <v>34392.68</v>
+        <v>1249081.56</v>
       </c>
       <c r="Q46" t="s">
         <v>512</v>
@@ -4089,19 +4086,19 @@
         <v>297</v>
       </c>
       <c r="D47" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E47" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F47" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="H47">
-        <v>534.6565721999999</v>
+        <v>847.6262729999999</v>
       </c>
       <c r="I47">
-        <v>7</v>
+        <v>168</v>
       </c>
       <c r="J47" t="s">
         <v>511</v>
@@ -4110,16 +4107,16 @@
         <v>33</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P47">
-        <v>5818.44</v>
+        <v>184655.09</v>
       </c>
       <c r="Q47" t="s">
         <v>512</v>
@@ -4136,19 +4133,19 @@
         <v>297</v>
       </c>
       <c r="D48" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E48" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F48" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="H48">
-        <v>1499.646483</v>
+        <v>612.8989974</v>
       </c>
       <c r="I48">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="J48" t="s">
         <v>511</v>
@@ -4157,16 +4154,16 @@
         <v>33</v>
       </c>
       <c r="M48">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="O48">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P48">
-        <v>385178.52</v>
+        <v>181542.17</v>
       </c>
       <c r="Q48" t="s">
         <v>512</v>
@@ -4183,19 +4180,19 @@
         <v>297</v>
       </c>
       <c r="D49" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="E49" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F49" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="H49">
-        <v>2803.686903</v>
+        <v>2585.9936</v>
       </c>
       <c r="I49">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J49" t="s">
         <v>511</v>
@@ -4207,13 +4204,13 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P49">
-        <v>34447.2</v>
+        <v>62918.27</v>
       </c>
       <c r="Q49" t="s">
         <v>512</v>
@@ -4230,19 +4227,19 @@
         <v>297</v>
       </c>
       <c r="D50" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E50" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F50" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="H50">
-        <v>1828.2802</v>
+        <v>2870.1202068</v>
       </c>
       <c r="I50">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="J50" t="s">
         <v>511</v>
@@ -4251,16 +4248,16 @@
         <v>33</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P50">
-        <v>211389.98</v>
+        <v>20972.02</v>
       </c>
       <c r="Q50" t="s">
         <v>512</v>
@@ -4277,7 +4274,7 @@
         <v>297</v>
       </c>
       <c r="D51" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E51" t="s">
         <v>437</v>
@@ -4286,10 +4283,10 @@
         <v>437</v>
       </c>
       <c r="H51">
-        <v>2179.9269789525</v>
+        <v>1956.06063</v>
       </c>
       <c r="I51">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="J51" t="s">
         <v>511</v>
@@ -4298,16 +4295,16 @@
         <v>33</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N51">
+        <v>1</v>
+      </c>
+      <c r="O51">
         <v>9</v>
       </c>
-      <c r="O51">
-        <v>8</v>
-      </c>
       <c r="P51">
-        <v>108043.59</v>
+        <v>181046.2</v>
       </c>
       <c r="Q51" t="s">
         <v>512</v>
@@ -4324,19 +4321,19 @@
         <v>297</v>
       </c>
       <c r="D52" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E52" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="F52" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="H52">
-        <v>2585.9936</v>
+        <v>708</v>
       </c>
       <c r="I52">
-        <v>15</v>
+        <v>268</v>
       </c>
       <c r="J52" t="s">
         <v>511</v>
@@ -4345,16 +4342,16 @@
         <v>33</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P52">
-        <v>62918.27</v>
+        <v>257061.79</v>
       </c>
       <c r="Q52" t="s">
         <v>512</v>
@@ -4371,19 +4368,19 @@
         <v>297</v>
       </c>
       <c r="D53" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E53" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F53" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="H53">
-        <v>912.8282939999998</v>
+        <v>521.6161679999999</v>
       </c>
       <c r="I53">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J53" t="s">
         <v>511</v>
@@ -4392,16 +4389,16 @@
         <v>33</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>28653.82</v>
+        <v>16881.32</v>
       </c>
       <c r="Q53" t="s">
         <v>512</v>
@@ -4418,19 +4415,19 @@
         <v>297</v>
       </c>
       <c r="D54" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E54" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F54" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="H54">
-        <v>874.2436631991176</v>
+        <v>179.9635942941177</v>
       </c>
       <c r="I54">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="J54" t="s">
         <v>511</v>
@@ -4439,16 +4436,16 @@
         <v>33</v>
       </c>
       <c r="M54">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="P54">
-        <v>56045.04</v>
+        <v>19208.47</v>
       </c>
       <c r="Q54" t="s">
         <v>512</v>
@@ -4465,19 +4462,19 @@
         <v>297</v>
       </c>
       <c r="D55" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E55" t="s">
         <v>443</v>
       </c>
       <c r="F55" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="H55">
-        <v>1107.780080664706</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I55">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="J55" t="s">
         <v>511</v>
@@ -4486,16 +4483,16 @@
         <v>33</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N55">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O55">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>35130.13</v>
+        <v>111781.83</v>
       </c>
       <c r="Q55" t="s">
         <v>512</v>
@@ -4512,19 +4509,19 @@
         <v>297</v>
       </c>
       <c r="D56" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E56" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F56" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="H56">
-        <v>2738.484882</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I56">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J56" t="s">
         <v>511</v>
@@ -4533,16 +4530,16 @@
         <v>33</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N56">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>61616.29</v>
+        <v>11853.18</v>
       </c>
       <c r="Q56" t="s">
         <v>512</v>
@@ -4559,19 +4556,19 @@
         <v>297</v>
       </c>
       <c r="D57" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E57" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="F57" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="H57">
-        <v>3748.5845172</v>
+        <v>1305.459898830882</v>
       </c>
       <c r="I57">
-        <v>189</v>
+        <v>6</v>
       </c>
       <c r="J57" t="s">
         <v>511</v>
@@ -4580,16 +4577,16 @@
         <v>33</v>
       </c>
       <c r="M57">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P57">
-        <v>976309.37</v>
+        <v>10062.28</v>
       </c>
       <c r="Q57" t="s">
         <v>512</v>
@@ -4606,19 +4603,19 @@
         <v>297</v>
       </c>
       <c r="D58" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E58" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F58" t="s">
         <v>479</v>
       </c>
       <c r="H58">
-        <v>2975.579697881559</v>
+        <v>9527.5088</v>
       </c>
       <c r="I58">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J58" t="s">
         <v>511</v>
@@ -4630,13 +4627,13 @@
         <v>0</v>
       </c>
       <c r="N58">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P58">
-        <v>82001.02</v>
+        <v>328613.64</v>
       </c>
       <c r="Q58" t="s">
         <v>512</v>
@@ -4653,7 +4650,7 @@
         <v>297</v>
       </c>
       <c r="D59" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E59" t="s">
         <v>432</v>
@@ -4662,10 +4659,10 @@
         <v>480</v>
       </c>
       <c r="H59">
-        <v>4180.2798</v>
+        <v>734.122339149</v>
       </c>
       <c r="I59">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J59" t="s">
         <v>511</v>
@@ -4674,16 +4671,16 @@
         <v>33</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N59">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P59">
-        <v>87530.92999999999</v>
+        <v>49886.64</v>
       </c>
       <c r="Q59" t="s">
         <v>512</v>
@@ -4700,19 +4697,19 @@
         <v>297</v>
       </c>
       <c r="D60" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E60" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F60" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="H60">
-        <v>326.010105</v>
+        <v>7722.439199999999</v>
       </c>
       <c r="I60">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="J60" t="s">
         <v>511</v>
@@ -4721,16 +4718,16 @@
         <v>33</v>
       </c>
       <c r="M60">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>29143.7</v>
+        <v>134448.52</v>
       </c>
       <c r="Q60" t="s">
         <v>512</v>
@@ -4747,19 +4744,19 @@
         <v>297</v>
       </c>
       <c r="D61" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E61" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F61" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="H61">
-        <v>3040.14077289</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I61">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="J61" t="s">
         <v>511</v>
@@ -4768,16 +4765,16 @@
         <v>33</v>
       </c>
       <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
         <v>5</v>
       </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
       <c r="O61">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P61">
-        <v>247477.55</v>
+        <v>12578.82</v>
       </c>
       <c r="Q61" t="s">
         <v>512</v>
@@ -4794,19 +4791,19 @@
         <v>297</v>
       </c>
       <c r="D62" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E62" t="s">
         <v>445</v>
       </c>
       <c r="F62" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
       <c r="H62">
-        <v>2664.193308210882</v>
+        <v>678.1010183999999</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J62" t="s">
         <v>511</v>
@@ -4815,13 +4812,16 @@
         <v>33</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="P62">
+        <v>63167.25</v>
       </c>
       <c r="Q62" t="s">
         <v>512</v>
@@ -4838,19 +4838,19 @@
         <v>297</v>
       </c>
       <c r="D63" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E63" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H63">
-        <v>1679.60406096</v>
+        <v>3065.101673616</v>
       </c>
       <c r="I63">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="J63" t="s">
         <v>511</v>
@@ -4859,16 +4859,16 @@
         <v>33</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N63">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P63">
-        <v>422763.4</v>
+        <v>657723.2</v>
       </c>
       <c r="Q63" t="s">
         <v>512</v>
@@ -4885,19 +4885,19 @@
         <v>297</v>
       </c>
       <c r="D64" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E64" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="F64" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="H64">
-        <v>1679.6</v>
+        <v>920.65253652</v>
       </c>
       <c r="I64">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J64" t="s">
         <v>511</v>
@@ -4906,16 +4906,16 @@
         <v>33</v>
       </c>
       <c r="M64">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="N64">
         <v>0</v>
       </c>
       <c r="O64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P64">
-        <v>64518.64</v>
+        <v>9294.129999999999</v>
       </c>
       <c r="Q64" t="s">
         <v>512</v>
@@ -4932,19 +4932,19 @@
         <v>297</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="E65" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F65" t="s">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="H65">
-        <v>1159.29193338</v>
+        <v>1304.04042</v>
       </c>
       <c r="I65">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="J65" t="s">
         <v>511</v>
@@ -4953,16 +4953,16 @@
         <v>33</v>
       </c>
       <c r="M65">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="P65">
-        <v>69637.41</v>
+        <v>181432.26</v>
       </c>
       <c r="Q65" t="s">
         <v>512</v>
@@ -4979,19 +4979,19 @@
         <v>297</v>
       </c>
       <c r="D66" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E66" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="F66" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H66">
-        <v>5118.2854</v>
+        <v>2311.522194589411</v>
       </c>
       <c r="I66">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J66" t="s">
         <v>511</v>
@@ -5000,16 +5000,16 @@
         <v>33</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N66">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66">
-        <v>120811.9</v>
+        <v>69659.17999999999</v>
       </c>
       <c r="Q66" t="s">
         <v>512</v>
@@ -5026,19 +5026,19 @@
         <v>297</v>
       </c>
       <c r="D67" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E67" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="F67" t="s">
-        <v>484</v>
+        <v>458</v>
       </c>
       <c r="H67">
-        <v>7722.439199999999</v>
+        <v>1679.6</v>
       </c>
       <c r="I67">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J67" t="s">
         <v>511</v>
@@ -5047,16 +5047,16 @@
         <v>33</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N67">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>124170.87</v>
+        <v>64518.64</v>
       </c>
       <c r="Q67" t="s">
         <v>512</v>
@@ -5073,19 +5073,19 @@
         <v>297</v>
       </c>
       <c r="D68" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E68" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="F68" t="s">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="H68">
-        <v>4696.526757959999</v>
+        <v>2157.615343358823</v>
       </c>
       <c r="I68">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J68" t="s">
         <v>511</v>
@@ -5097,13 +5097,10 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O68">
         <v>0</v>
-      </c>
-      <c r="P68">
-        <v>66417.75</v>
       </c>
       <c r="Q68" t="s">
         <v>512</v>
@@ -5120,19 +5117,19 @@
         <v>297</v>
       </c>
       <c r="D69" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="E69" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F69" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="H69">
-        <v>2164.7070972</v>
+        <v>1544.91011775</v>
       </c>
       <c r="I69">
-        <v>8</v>
+        <v>663</v>
       </c>
       <c r="J69" t="s">
         <v>511</v>
@@ -5144,13 +5141,13 @@
         <v>0</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P69">
-        <v>11853.18</v>
+        <v>1417340.71</v>
       </c>
       <c r="Q69" t="s">
         <v>512</v>
@@ -5167,19 +5164,19 @@
         <v>297</v>
       </c>
       <c r="D70" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E70" t="s">
         <v>432</v>
       </c>
       <c r="F70" t="s">
-        <v>486</v>
+        <v>451</v>
       </c>
       <c r="H70">
-        <v>2280.5034</v>
+        <v>1475.964687829412</v>
       </c>
       <c r="I70">
-        <v>11</v>
+        <v>1887</v>
       </c>
       <c r="J70" t="s">
         <v>511</v>
@@ -5188,16 +5185,16 @@
         <v>33</v>
       </c>
       <c r="M70">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="O70">
-        <v>4</v>
+        <v>224</v>
       </c>
       <c r="P70">
-        <v>44601.81</v>
+        <v>3590722.61</v>
       </c>
       <c r="Q70" t="s">
         <v>512</v>
@@ -5214,19 +5211,19 @@
         <v>297</v>
       </c>
       <c r="D71" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E71" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="F71" t="s">
-        <v>487</v>
+        <v>437</v>
       </c>
       <c r="H71">
-        <v>2630.5268</v>
+        <v>2263.0394</v>
       </c>
       <c r="I71">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J71" t="s">
         <v>511</v>
@@ -5238,13 +5235,13 @@
         <v>0</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>83470.71000000001</v>
+        <v>32855.75</v>
       </c>
       <c r="Q71" t="s">
         <v>512</v>
@@ -5261,19 +5258,19 @@
         <v>297</v>
       </c>
       <c r="D72" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E72" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="F72" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="H72">
-        <v>756.3434436</v>
+        <v>4486.010979600001</v>
       </c>
       <c r="I72">
-        <v>42</v>
+        <v>337</v>
       </c>
       <c r="J72" t="s">
         <v>511</v>
@@ -5282,16 +5279,16 @@
         <v>33</v>
       </c>
       <c r="M72">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N72">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="O72">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="P72">
-        <v>42013.28</v>
+        <v>2425594.88</v>
       </c>
       <c r="Q72" t="s">
         <v>512</v>
@@ -5308,19 +5305,19 @@
         <v>297</v>
       </c>
       <c r="D73" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E73" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="F73" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="H73">
-        <v>1960.237563966397</v>
+        <v>4694.545512</v>
       </c>
       <c r="I73">
-        <v>196</v>
+        <v>11</v>
       </c>
       <c r="J73" t="s">
         <v>511</v>
@@ -5329,16 +5326,16 @@
         <v>33</v>
       </c>
       <c r="M73">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N73">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O73">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P73">
-        <v>520601.56</v>
+        <v>65368.26</v>
       </c>
       <c r="Q73" t="s">
         <v>512</v>
@@ -5355,19 +5352,19 @@
         <v>297</v>
       </c>
       <c r="D74" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E74" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F74" t="s">
         <v>488</v>
       </c>
       <c r="H74">
-        <v>5836.846399999999</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I74">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J74" t="s">
         <v>511</v>
@@ -5376,16 +5373,16 @@
         <v>33</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P74">
-        <v>205552.34</v>
+        <v>74737.64999999999</v>
       </c>
       <c r="Q74" t="s">
         <v>512</v>
@@ -5402,19 +5399,19 @@
         <v>297</v>
       </c>
       <c r="D75" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E75" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="F75" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="H75">
-        <v>130.404042</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I75">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J75" t="s">
         <v>511</v>
@@ -5423,16 +5420,16 @@
         <v>33</v>
       </c>
       <c r="M75">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N75">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>11515.93</v>
+        <v>34079.43</v>
       </c>
       <c r="Q75" t="s">
         <v>512</v>
@@ -5449,19 +5446,19 @@
         <v>297</v>
       </c>
       <c r="D76" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E76" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F76" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="H76">
-        <v>503.35960212</v>
+        <v>905.00405148</v>
       </c>
       <c r="I76">
-        <v>128</v>
+        <v>19</v>
       </c>
       <c r="J76" t="s">
         <v>511</v>
@@ -5470,16 +5467,16 @@
         <v>33</v>
       </c>
       <c r="M76">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P76">
-        <v>122775.78</v>
+        <v>25590.84</v>
       </c>
       <c r="Q76" t="s">
         <v>512</v>
@@ -5496,19 +5493,19 @@
         <v>297</v>
       </c>
       <c r="D77" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E77" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F77" t="s">
-        <v>490</v>
+        <v>461</v>
       </c>
       <c r="H77">
-        <v>3196.1775</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I77">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J77" t="s">
         <v>511</v>
@@ -5517,16 +5514,16 @@
         <v>33</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>3165.42</v>
+        <v>37374.55</v>
       </c>
       <c r="Q77" t="s">
         <v>512</v>
@@ -5543,13 +5540,13 @@
         <v>297</v>
       </c>
       <c r="D78" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E78" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F78" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H78">
         <v>2173.4007</v>
@@ -5590,19 +5587,19 @@
         <v>297</v>
       </c>
       <c r="D79" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E79" t="s">
         <v>435</v>
       </c>
       <c r="F79" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H79">
-        <v>521.6161679999999</v>
+        <v>1194.50102472</v>
       </c>
       <c r="I79">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J79" t="s">
         <v>511</v>
@@ -5611,16 +5608,16 @@
         <v>33</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N79">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P79">
-        <v>17384.27</v>
+        <v>41216.62</v>
       </c>
       <c r="Q79" t="s">
         <v>512</v>
@@ -5637,19 +5634,19 @@
         <v>297</v>
       </c>
       <c r="D80" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E80" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="F80" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="H80">
-        <v>6152.0362</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I80">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J80" t="s">
         <v>511</v>
@@ -5658,16 +5655,16 @@
         <v>33</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80">
-        <v>184995.63</v>
+        <v>74082.34</v>
       </c>
       <c r="Q80" t="s">
         <v>512</v>
@@ -5684,19 +5681,19 @@
         <v>297</v>
       </c>
       <c r="D81" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E81" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="F81" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="H81">
-        <v>477.9615959999999</v>
+        <v>130.404042</v>
       </c>
       <c r="I81">
-        <v>181</v>
+        <v>33</v>
       </c>
       <c r="J81" t="s">
         <v>511</v>
@@ -5705,16 +5702,16 @@
         <v>33</v>
       </c>
       <c r="M81">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N81">
+        <v>11</v>
+      </c>
+      <c r="O81">
         <v>1</v>
       </c>
-      <c r="O81">
-        <v>10</v>
-      </c>
       <c r="P81">
-        <v>174987.05</v>
+        <v>11515.93</v>
       </c>
       <c r="Q81" t="s">
         <v>512</v>
@@ -5731,19 +5728,19 @@
         <v>297</v>
       </c>
       <c r="D82" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E82" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="F82" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="H82">
-        <v>1201.7320128</v>
+        <v>2458.088208</v>
       </c>
       <c r="I82">
-        <v>651</v>
+        <v>7</v>
       </c>
       <c r="J82" t="s">
         <v>511</v>
@@ -5752,16 +5749,16 @@
         <v>33</v>
       </c>
       <c r="M82">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="N82">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O82">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="P82">
-        <v>964552.22</v>
+        <v>21530.69</v>
       </c>
       <c r="Q82" t="s">
         <v>512</v>
@@ -5778,19 +5775,19 @@
         <v>297</v>
       </c>
       <c r="D83" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E83" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F83" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="H83">
-        <v>7169.514799999999</v>
+        <v>6259.394015999999</v>
       </c>
       <c r="I83">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J83" t="s">
         <v>511</v>
@@ -5802,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="N83">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>111515.92</v>
+        <v>142206.19</v>
       </c>
       <c r="Q83" t="s">
         <v>512</v>
@@ -5825,19 +5822,19 @@
         <v>297</v>
       </c>
       <c r="D84" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E84" t="s">
         <v>440</v>
       </c>
       <c r="F84" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="H84">
-        <v>1291.959696295941</v>
+        <v>2803.686903</v>
       </c>
       <c r="I84">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="J84" t="s">
         <v>511</v>
@@ -5846,16 +5843,16 @@
         <v>33</v>
       </c>
       <c r="M84">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N84">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>164659.41</v>
+        <v>34447.2</v>
       </c>
       <c r="Q84" t="s">
         <v>512</v>
@@ -5872,19 +5869,19 @@
         <v>297</v>
       </c>
       <c r="D85" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E85" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F85" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="H85">
-        <v>3998.590893</v>
+        <v>1828.2802</v>
       </c>
       <c r="I85">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="J85" t="s">
         <v>511</v>
@@ -5893,16 +5890,16 @@
         <v>33</v>
       </c>
       <c r="M85">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N85">
         <v>0</v>
       </c>
       <c r="O85">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P85">
-        <v>242453.7</v>
+        <v>196710.12</v>
       </c>
       <c r="Q85" t="s">
         <v>512</v>
@@ -5919,19 +5916,19 @@
         <v>297</v>
       </c>
       <c r="D86" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E86" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F86" t="s">
-        <v>478</v>
+        <v>436</v>
       </c>
       <c r="H86">
-        <v>4486.010979600001</v>
+        <v>477.9615959999999</v>
       </c>
       <c r="I86">
-        <v>346</v>
+        <v>180</v>
       </c>
       <c r="J86" t="s">
         <v>511</v>
@@ -5943,13 +5940,13 @@
         <v>20</v>
       </c>
       <c r="N86">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="P86">
-        <v>2487118.84</v>
+        <v>174059.87</v>
       </c>
       <c r="Q86" t="s">
         <v>512</v>
@@ -5966,19 +5963,19 @@
         <v>297</v>
       </c>
       <c r="D87" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E87" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F87" t="s">
-        <v>495</v>
+        <v>453</v>
       </c>
       <c r="H87">
-        <v>9527.5088</v>
+        <v>1107.780080664706</v>
       </c>
       <c r="I87">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J87" t="s">
         <v>511</v>
@@ -5990,13 +5987,13 @@
         <v>0</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O87">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P87">
-        <v>328613.64</v>
+        <v>35130.13</v>
       </c>
       <c r="Q87" t="s">
         <v>512</v>
@@ -6013,19 +6010,19 @@
         <v>297</v>
       </c>
       <c r="D88" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E88" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="F88" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H88">
-        <v>612.8989974</v>
+        <v>2021.262651</v>
       </c>
       <c r="I88">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="J88" t="s">
         <v>511</v>
@@ -6034,16 +6031,16 @@
         <v>33</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N88">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="O88">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P88">
-        <v>182414.97</v>
+        <v>69360.06</v>
       </c>
       <c r="Q88" t="s">
         <v>512</v>
@@ -6060,19 +6057,19 @@
         <v>297</v>
       </c>
       <c r="D89" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E89" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F89" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H89">
-        <v>2119.874127397059</v>
+        <v>4180.2798</v>
       </c>
       <c r="I89">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="J89" t="s">
         <v>511</v>
@@ -6084,13 +6081,13 @@
         <v>0</v>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>331764.83</v>
+        <v>87530.92999999999</v>
       </c>
       <c r="Q89" t="s">
         <v>512</v>
@@ -6107,19 +6104,19 @@
         <v>297</v>
       </c>
       <c r="D90" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E90" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F90" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="H90">
-        <v>4119.760313999999</v>
+        <v>598.3056269558823</v>
       </c>
       <c r="I90">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="J90" t="s">
         <v>511</v>
@@ -6128,16 +6125,16 @@
         <v>33</v>
       </c>
       <c r="M90">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O90">
         <v>13</v>
       </c>
       <c r="P90">
-        <v>521758.56</v>
+        <v>25211.62</v>
       </c>
       <c r="Q90" t="s">
         <v>512</v>
@@ -6154,19 +6151,19 @@
         <v>297</v>
       </c>
       <c r="D91" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E91" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F91" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H91">
-        <v>1983.58</v>
+        <v>1825.656588</v>
       </c>
       <c r="I91">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J91" t="s">
         <v>511</v>
@@ -6175,16 +6172,16 @@
         <v>33</v>
       </c>
       <c r="M91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N91">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O91">
         <v>0</v>
       </c>
       <c r="P91">
-        <v>51100.26</v>
+        <v>40263.18</v>
       </c>
       <c r="Q91" t="s">
         <v>512</v>
@@ -6201,19 +6198,19 @@
         <v>297</v>
       </c>
       <c r="D92" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E92" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="F92" t="s">
-        <v>447</v>
+        <v>495</v>
       </c>
       <c r="H92">
-        <v>614.5220519999999</v>
+        <v>3998.590893</v>
       </c>
       <c r="I92">
-        <v>273</v>
+        <v>42</v>
       </c>
       <c r="J92" t="s">
         <v>511</v>
@@ -6222,16 +6219,16 @@
         <v>33</v>
       </c>
       <c r="M92">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="N92">
         <v>0</v>
       </c>
       <c r="O92">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="P92">
-        <v>304983.64</v>
+        <v>226094.34</v>
       </c>
       <c r="Q92" t="s">
         <v>512</v>
@@ -6248,19 +6245,19 @@
         <v>297</v>
       </c>
       <c r="D93" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E93" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F93" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="H93">
-        <v>5808.86204274</v>
+        <v>13162.63420323</v>
       </c>
       <c r="I93">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J93" t="s">
         <v>511</v>
@@ -6269,16 +6266,16 @@
         <v>33</v>
       </c>
       <c r="M93">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N93">
         <v>0</v>
       </c>
       <c r="O93">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>167795.85</v>
+        <v>17479.49</v>
       </c>
       <c r="Q93" t="s">
         <v>512</v>
@@ -6295,19 +6292,19 @@
         <v>297</v>
       </c>
       <c r="D94" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E94" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F94" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="H94">
-        <v>659.7098370441175</v>
+        <v>1043.232336</v>
       </c>
       <c r="I94">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="J94" t="s">
         <v>511</v>
@@ -6316,16 +6313,16 @@
         <v>33</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N94">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>33896.96</v>
+        <v>14949.82</v>
       </c>
       <c r="Q94" t="s">
         <v>512</v>
@@ -6342,19 +6339,19 @@
         <v>297</v>
       </c>
       <c r="D95" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E95" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="F95" t="s">
-        <v>500</v>
+        <v>453</v>
       </c>
       <c r="H95">
-        <v>2870.1202068</v>
+        <v>1960.237563966397</v>
       </c>
       <c r="I95">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="J95" t="s">
         <v>511</v>
@@ -6363,16 +6360,16 @@
         <v>33</v>
       </c>
       <c r="M95">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="N95">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O95">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P95">
-        <v>20972.02</v>
+        <v>510192.26</v>
       </c>
       <c r="Q95" t="s">
         <v>512</v>
@@ -6389,19 +6386,19 @@
         <v>297</v>
       </c>
       <c r="D96" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E96" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="F96" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="H96">
-        <v>2436.8652</v>
+        <v>503.35960212</v>
       </c>
       <c r="I96">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="J96" t="s">
         <v>511</v>
@@ -6410,16 +6407,16 @@
         <v>33</v>
       </c>
       <c r="M96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N96">
         <v>0</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P96">
-        <v>111364.9</v>
+        <v>116061.48</v>
       </c>
       <c r="Q96" t="s">
         <v>512</v>
@@ -6436,19 +6433,19 @@
         <v>297</v>
       </c>
       <c r="D97" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E97" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="F97" t="s">
-        <v>502</v>
+        <v>442</v>
       </c>
       <c r="H97">
-        <v>3358.8228</v>
+        <v>1092.483648</v>
       </c>
       <c r="I97">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J97" t="s">
         <v>511</v>
@@ -6460,13 +6457,13 @@
         <v>0</v>
       </c>
       <c r="N97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O97">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P97">
-        <v>5033.59</v>
+        <v>41823.6</v>
       </c>
       <c r="Q97" t="s">
         <v>512</v>
@@ -6483,37 +6480,37 @@
         <v>297</v>
       </c>
       <c r="D98" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E98" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="F98" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="H98">
-        <v>1092.483648</v>
+        <v>659.7098370441175</v>
       </c>
       <c r="I98">
+        <v>51</v>
+      </c>
+      <c r="J98" t="s">
+        <v>511</v>
+      </c>
+      <c r="L98">
+        <v>33</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
         <v>23</v>
       </c>
-      <c r="J98" t="s">
-        <v>511</v>
-      </c>
-      <c r="L98">
-        <v>33</v>
-      </c>
-      <c r="M98">
-        <v>6</v>
-      </c>
-      <c r="N98">
-        <v>2</v>
-      </c>
       <c r="O98">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P98">
-        <v>35627.51</v>
+        <v>33896.96</v>
       </c>
       <c r="Q98" t="s">
         <v>512</v>
@@ -6530,19 +6527,19 @@
         <v>297</v>
       </c>
       <c r="D99" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E99" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F99" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="H99">
-        <v>2165.574481998618</v>
+        <v>2934.090945</v>
       </c>
       <c r="I99">
-        <v>832</v>
+        <v>11</v>
       </c>
       <c r="J99" t="s">
         <v>511</v>
@@ -6551,16 +6548,16 @@
         <v>33</v>
       </c>
       <c r="M99">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="N99">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="O99">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="P99">
-        <v>2990592.91</v>
+        <v>28257.82</v>
       </c>
       <c r="Q99" t="s">
         <v>512</v>
@@ -6577,19 +6574,19 @@
         <v>297</v>
       </c>
       <c r="D100" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E100" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F100" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="H100">
-        <v>3277.450944</v>
+        <v>827.5708984229998</v>
       </c>
       <c r="I100">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J100" t="s">
         <v>511</v>
@@ -6601,13 +6598,13 @@
         <v>0</v>
       </c>
       <c r="N100">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>81023.5</v>
+        <v>2014.34</v>
       </c>
       <c r="Q100" t="s">
         <v>512</v>
@@ -6624,19 +6621,19 @@
         <v>297</v>
       </c>
       <c r="D101" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E101" t="s">
         <v>435</v>
       </c>
       <c r="F101" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="H101">
-        <v>3140.890488</v>
+        <v>2360.3131602</v>
       </c>
       <c r="I101">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="J101" t="s">
         <v>511</v>
@@ -6645,16 +6642,16 @@
         <v>33</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="O101">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>245376.18</v>
+        <v>31526.62</v>
       </c>
       <c r="Q101" t="s">
         <v>512</v>
@@ -6671,19 +6668,19 @@
         <v>297</v>
       </c>
       <c r="D102" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E102" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="F102" t="s">
-        <v>503</v>
+        <v>450</v>
       </c>
       <c r="H102">
-        <v>1544.91011775</v>
+        <v>1700.734990628047</v>
       </c>
       <c r="I102">
-        <v>672</v>
+        <v>5</v>
       </c>
       <c r="J102" t="s">
         <v>511</v>
@@ -6692,16 +6689,16 @@
         <v>33</v>
       </c>
       <c r="M102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O102">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="P102">
-        <v>1436470.06</v>
+        <v>7893.34</v>
       </c>
       <c r="Q102" t="s">
         <v>512</v>
@@ -6718,19 +6715,19 @@
         <v>297</v>
       </c>
       <c r="D103" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E103" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="F103" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="H103">
-        <v>1722.835557825</v>
+        <v>2975.579697881559</v>
       </c>
       <c r="I103">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="J103" t="s">
         <v>511</v>
@@ -6739,16 +6736,16 @@
         <v>33</v>
       </c>
       <c r="M103">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O103">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P103">
-        <v>119407.65</v>
+        <v>82001.02</v>
       </c>
       <c r="Q103" t="s">
         <v>512</v>
@@ -6765,19 +6762,19 @@
         <v>297</v>
       </c>
       <c r="D104" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E104" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F104" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="H104">
-        <v>2021.262651</v>
+        <v>4841.8232</v>
       </c>
       <c r="I104">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J104" t="s">
         <v>511</v>
@@ -6786,16 +6783,16 @@
         <v>33</v>
       </c>
       <c r="M104">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N104">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O104">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>59084.49</v>
+        <v>111163.58</v>
       </c>
       <c r="Q104" t="s">
         <v>512</v>
@@ -6812,19 +6809,19 @@
         <v>297</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E105" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="F105" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="H105">
-        <v>2973.2121576</v>
+        <v>2738.484882</v>
       </c>
       <c r="I105">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J105" t="s">
         <v>511</v>
@@ -6836,13 +6833,13 @@
         <v>3</v>
       </c>
       <c r="N105">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O105">
         <v>3</v>
       </c>
       <c r="P105">
-        <v>52265.13</v>
+        <v>61616.29</v>
       </c>
       <c r="Q105" t="s">
         <v>512</v>
@@ -6859,19 +6856,19 @@
         <v>297</v>
       </c>
       <c r="D106" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E106" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="F106" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="H106">
-        <v>2157.615343358823</v>
+        <v>3748.5845172</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="J106" t="s">
         <v>511</v>
@@ -6880,13 +6877,16 @@
         <v>33</v>
       </c>
       <c r="M106">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="N106">
         <v>0</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="P106">
+        <v>899756.6800000001</v>
       </c>
       <c r="Q106" t="s">
         <v>512</v>
@@ -6903,19 +6903,19 @@
         <v>297</v>
       </c>
       <c r="D107" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E107" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="F107" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="H107">
-        <v>1092.483648</v>
+        <v>2261.3068296</v>
       </c>
       <c r="I107">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J107" t="s">
         <v>511</v>
@@ -6924,16 +6924,16 @@
         <v>33</v>
       </c>
       <c r="M107">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N107">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O107">
         <v>2</v>
       </c>
       <c r="P107">
-        <v>69706.00999999999</v>
+        <v>56971.2</v>
       </c>
       <c r="Q107" t="s">
         <v>512</v>
@@ -6950,19 +6950,19 @@
         <v>297</v>
       </c>
       <c r="D108" t="s">
-        <v>399</v>
+        <v>310</v>
       </c>
       <c r="E108" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="F108" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="H108">
-        <v>1330.281037275</v>
+        <v>1499.646483</v>
       </c>
       <c r="I108">
-        <v>141</v>
+        <v>11</v>
       </c>
       <c r="J108" t="s">
         <v>511</v>
@@ -6971,16 +6971,16 @@
         <v>33</v>
       </c>
       <c r="M108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N108">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P108">
-        <v>238944.61</v>
+        <v>19633.36</v>
       </c>
       <c r="Q108" t="s">
         <v>512</v>
@@ -6997,19 +6997,19 @@
         <v>297</v>
       </c>
       <c r="D109" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E109" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F109" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H109">
-        <v>3835.413</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J109" t="s">
         <v>511</v>
@@ -7018,13 +7018,16 @@
         <v>33</v>
       </c>
       <c r="M109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="P109">
+        <v>104937.09</v>
       </c>
       <c r="Q109" t="s">
         <v>512</v>
@@ -7041,19 +7044,19 @@
         <v>297</v>
       </c>
       <c r="D110" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E110" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F110" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="H110">
-        <v>4986.467599999999</v>
+        <v>5118.2854</v>
       </c>
       <c r="I110">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="J110" t="s">
         <v>511</v>
@@ -7062,16 +7065,16 @@
         <v>33</v>
       </c>
       <c r="M110">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P110">
-        <v>679429.59</v>
+        <v>102773.72</v>
       </c>
       <c r="Q110" t="s">
         <v>512</v>
@@ -7088,19 +7091,19 @@
         <v>297</v>
       </c>
       <c r="D111" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="E111" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F111" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="H111">
-        <v>847.6262729999999</v>
+        <v>1043.232336</v>
       </c>
       <c r="I111">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="J111" t="s">
         <v>511</v>
@@ -7109,16 +7112,16 @@
         <v>33</v>
       </c>
       <c r="M111">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N111">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O111">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="P111">
-        <v>189099.69</v>
+        <v>48613.87</v>
       </c>
       <c r="Q111" t="s">
         <v>512</v>
@@ -7135,19 +7138,19 @@
         <v>297</v>
       </c>
       <c r="D112" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E112" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F112" t="s">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="H112">
-        <v>1475.964687829412</v>
+        <v>2119.874127397059</v>
       </c>
       <c r="I112">
-        <v>2225</v>
+        <v>113</v>
       </c>
       <c r="J112" t="s">
         <v>511</v>
@@ -7156,16 +7159,16 @@
         <v>33</v>
       </c>
       <c r="M112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N112">
-        <v>201</v>
+        <v>4</v>
       </c>
       <c r="O112">
-        <v>224</v>
+        <v>10</v>
       </c>
       <c r="P112">
-        <v>4239547.97</v>
+        <v>328828.86</v>
       </c>
       <c r="Q112" t="s">
         <v>512</v>
@@ -7182,19 +7185,19 @@
         <v>297</v>
       </c>
       <c r="D113" t="s">
-        <v>404</v>
+        <v>362</v>
       </c>
       <c r="E113" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F113" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="H113">
-        <v>260.808084</v>
+        <v>1679.60406096</v>
       </c>
       <c r="I113">
-        <v>308</v>
+        <v>167</v>
       </c>
       <c r="J113" t="s">
         <v>511</v>
@@ -7203,16 +7206,16 @@
         <v>33</v>
       </c>
       <c r="M113">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="O113">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P113">
-        <v>131700.92</v>
+        <v>420246.95</v>
       </c>
       <c r="Q113" t="s">
         <v>512</v>
@@ -7229,19 +7232,19 @@
         <v>297</v>
       </c>
       <c r="D114" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E114" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F114" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="H114">
-        <v>905.00405148</v>
+        <v>2165.574481998618</v>
       </c>
       <c r="I114">
-        <v>21</v>
+        <v>822</v>
       </c>
       <c r="J114" t="s">
         <v>511</v>
@@ -7250,16 +7253,16 @@
         <v>33</v>
       </c>
       <c r="M114">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N114">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="O114">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="P114">
-        <v>28284.61</v>
+        <v>2954800.48</v>
       </c>
       <c r="Q114" t="s">
         <v>512</v>
@@ -7276,19 +7279,19 @@
         <v>297</v>
       </c>
       <c r="D115" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E115" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F115" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H115">
-        <v>1956.963080117647</v>
+        <v>4934.296426588235</v>
       </c>
       <c r="I115">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="J115" t="s">
         <v>511</v>
@@ -7297,16 +7300,16 @@
         <v>33</v>
       </c>
       <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>6</v>
+      </c>
+      <c r="O115">
         <v>1</v>
       </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>2</v>
-      </c>
       <c r="P115">
-        <v>91015.13</v>
+        <v>21111.87</v>
       </c>
       <c r="Q115" t="s">
         <v>512</v>
@@ -7323,19 +7326,19 @@
         <v>297</v>
       </c>
       <c r="D116" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E116" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="F116" t="s">
-        <v>505</v>
+        <v>445</v>
       </c>
       <c r="H116">
-        <v>3425.8468</v>
+        <v>1499.646483</v>
       </c>
       <c r="I116">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="J116" t="s">
         <v>511</v>
@@ -7344,16 +7347,16 @@
         <v>33</v>
       </c>
       <c r="M116">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N116">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P116">
-        <v>15450.38</v>
+        <v>385178.52</v>
       </c>
       <c r="Q116" t="s">
         <v>512</v>
@@ -7370,19 +7373,19 @@
         <v>297</v>
       </c>
       <c r="D117" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E117" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F117" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="H117">
-        <v>598.3056269558823</v>
+        <v>3425.8468</v>
       </c>
       <c r="I117">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="J117" t="s">
         <v>511</v>
@@ -7391,16 +7394,16 @@
         <v>33</v>
       </c>
       <c r="M117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O117">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>26145.39</v>
+        <v>15450.38</v>
       </c>
       <c r="Q117" t="s">
         <v>512</v>
@@ -7417,19 +7420,19 @@
         <v>297</v>
       </c>
       <c r="D118" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E118" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F118" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H118">
-        <v>1305.459898830882</v>
+        <v>1984.74951924</v>
       </c>
       <c r="I118">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J118" t="s">
         <v>511</v>
@@ -7438,16 +7441,16 @@
         <v>33</v>
       </c>
       <c r="M118">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N118">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O118">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P118">
-        <v>11678.69</v>
+        <v>44048.43</v>
       </c>
       <c r="Q118" t="s">
         <v>512</v>
@@ -7464,19 +7467,19 @@
         <v>297</v>
       </c>
       <c r="D119" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E119" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F119" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="H119">
-        <v>280.0829144294117</v>
+        <v>1043.232336</v>
       </c>
       <c r="I119">
-        <v>468</v>
+        <v>28</v>
       </c>
       <c r="J119" t="s">
         <v>511</v>
@@ -7485,16 +7488,16 @@
         <v>33</v>
       </c>
       <c r="M119">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N119">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="O119">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P119">
-        <v>218353.29</v>
+        <v>39599.34</v>
       </c>
       <c r="Q119" t="s">
         <v>512</v>
@@ -7511,19 +7514,19 @@
         <v>297</v>
       </c>
       <c r="D120" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E120" t="s">
         <v>433</v>
       </c>
       <c r="F120" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H120">
-        <v>1815.59502123</v>
+        <v>12112.09532316</v>
       </c>
       <c r="I120">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J120" t="s">
         <v>511</v>
@@ -7535,13 +7538,13 @@
         <v>0</v>
       </c>
       <c r="N120">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O120">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P120">
-        <v>11049.23</v>
+        <v>15731.47</v>
       </c>
       <c r="Q120" t="s">
         <v>512</v>
@@ -7558,19 +7561,19 @@
         <v>297</v>
       </c>
       <c r="D121" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E121" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F121" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="H121">
-        <v>179.9635942941177</v>
+        <v>4889.153</v>
       </c>
       <c r="I121">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="J121" t="s">
         <v>511</v>
@@ -7579,16 +7582,16 @@
         <v>33</v>
       </c>
       <c r="M121">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P121">
-        <v>19906.4</v>
+        <v>39150.73</v>
       </c>
       <c r="Q121" t="s">
         <v>512</v>
@@ -7605,19 +7608,19 @@
         <v>297</v>
       </c>
       <c r="D122" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E122" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F122" t="s">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="H122">
-        <v>2263.0394</v>
+        <v>2021.262651</v>
       </c>
       <c r="I122">
-        <v>10</v>
+        <v>256</v>
       </c>
       <c r="J122" t="s">
         <v>511</v>
@@ -7629,13 +7632,13 @@
         <v>0</v>
       </c>
       <c r="N122">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="P122">
-        <v>32855.75</v>
+        <v>680492.67</v>
       </c>
       <c r="Q122" t="s">
         <v>512</v>
@@ -7652,19 +7655,19 @@
         <v>297</v>
       </c>
       <c r="D123" t="s">
-        <v>309</v>
+        <v>415</v>
       </c>
       <c r="E123" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="F123" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="H123">
-        <v>1499.646483</v>
+        <v>756.3434436</v>
       </c>
       <c r="I123">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="J123" t="s">
         <v>511</v>
@@ -7673,16 +7676,16 @@
         <v>33</v>
       </c>
       <c r="M123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O123">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P123">
-        <v>19633.36</v>
+        <v>42972.45</v>
       </c>
       <c r="Q123" t="s">
         <v>512</v>
@@ -7699,16 +7702,16 @@
         <v>297</v>
       </c>
       <c r="D124" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E124" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="F124" t="s">
-        <v>496</v>
+        <v>454</v>
       </c>
       <c r="H124">
-        <v>4277.252577599999</v>
+        <v>4042.525302</v>
       </c>
       <c r="I124">
         <v>4</v>
@@ -7723,13 +7726,13 @@
         <v>0</v>
       </c>
       <c r="N124">
+        <v>4</v>
+      </c>
+      <c r="O124">
         <v>3</v>
       </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
       <c r="P124">
-        <v>14645.6</v>
+        <v>17896.93</v>
       </c>
       <c r="Q124" t="s">
         <v>512</v>
@@ -7746,19 +7749,19 @@
         <v>297</v>
       </c>
       <c r="D125" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E125" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F125" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="H125">
-        <v>1304.04042</v>
+        <v>4859.948</v>
       </c>
       <c r="I125">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="J125" t="s">
         <v>511</v>
@@ -7767,16 +7770,16 @@
         <v>33</v>
       </c>
       <c r="M125">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N125">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="O125">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="P125">
-        <v>248667.47</v>
+        <v>82498.16</v>
       </c>
       <c r="Q125" t="s">
         <v>512</v>
@@ -7793,19 +7796,19 @@
         <v>297</v>
       </c>
       <c r="D126" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E126" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F126" t="s">
-        <v>458</v>
+        <v>504</v>
       </c>
       <c r="H126">
-        <v>2857.758705882353</v>
+        <v>3196.1775</v>
       </c>
       <c r="I126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J126" t="s">
         <v>511</v>
@@ -7814,16 +7817,16 @@
         <v>33</v>
       </c>
       <c r="M126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3165.42</v>
       </c>
       <c r="Q126" t="s">
         <v>512</v>
@@ -7840,19 +7843,19 @@
         <v>297</v>
       </c>
       <c r="D127" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E127" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F127" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H127">
-        <v>1693.3496544</v>
+        <v>260.808084</v>
       </c>
       <c r="I127">
-        <v>50</v>
+        <v>264</v>
       </c>
       <c r="J127" t="s">
         <v>511</v>
@@ -7861,16 +7864,16 @@
         <v>33</v>
       </c>
       <c r="M127">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
         <v>8</v>
       </c>
-      <c r="O127">
-        <v>6</v>
-      </c>
       <c r="P127">
-        <v>111342.41</v>
+        <v>112500.67</v>
       </c>
       <c r="Q127" t="s">
         <v>512</v>
@@ -7887,19 +7890,19 @@
         <v>297</v>
       </c>
       <c r="D128" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E128" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="F128" t="s">
-        <v>460</v>
+        <v>505</v>
       </c>
       <c r="H128">
-        <v>13162.63420323</v>
+        <v>2664.193308210882</v>
       </c>
       <c r="I128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="s">
         <v>511</v>
@@ -7915,9 +7918,6 @@
       </c>
       <c r="O128">
         <v>0</v>
-      </c>
-      <c r="P128">
-        <v>17479.49</v>
       </c>
       <c r="Q128" t="s">
         <v>512</v>
@@ -7934,19 +7934,19 @@
         <v>297</v>
       </c>
       <c r="D129" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E129" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="F129" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="H129">
-        <v>1043.232336</v>
+        <v>2179.9269789525</v>
       </c>
       <c r="I129">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J129" t="s">
         <v>511</v>
@@ -7955,16 +7955,16 @@
         <v>33</v>
       </c>
       <c r="M129">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N129">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="O129">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P129">
-        <v>39599.34</v>
+        <v>102171.65</v>
       </c>
       <c r="Q129" t="s">
         <v>512</v>
@@ -7981,19 +7981,19 @@
         <v>297</v>
       </c>
       <c r="D130" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E130" t="s">
         <v>438</v>
       </c>
       <c r="F130" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="H130">
-        <v>3065.101673616</v>
+        <v>3317.4116676</v>
       </c>
       <c r="I130">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="J130" t="s">
         <v>511</v>
@@ -8002,16 +8002,16 @@
         <v>33</v>
       </c>
       <c r="M130">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N130">
         <v>0</v>
       </c>
       <c r="O130">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P130">
-        <v>718126.37</v>
+        <v>3844.94</v>
       </c>
       <c r="Q130" t="s">
         <v>512</v>
@@ -8028,19 +8028,19 @@
         <v>297</v>
       </c>
       <c r="D131" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E131" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F131" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="H131">
-        <v>920.65253652</v>
+        <v>1291.959696295941</v>
       </c>
       <c r="I131">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="J131" t="s">
         <v>511</v>
@@ -8049,16 +8049,16 @@
         <v>33</v>
       </c>
       <c r="M131">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="N131">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O131">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P131">
-        <v>10775.78</v>
+        <v>112124.66</v>
       </c>
       <c r="Q131" t="s">
         <v>512</v>
@@ -8075,19 +8075,19 @@
         <v>297</v>
       </c>
       <c r="D132" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E132" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F132" t="s">
-        <v>507</v>
+        <v>451</v>
       </c>
       <c r="H132">
-        <v>11761.9332</v>
+        <v>1693.3496544</v>
       </c>
       <c r="I132">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="J132" t="s">
         <v>511</v>
@@ -8099,13 +8099,13 @@
         <v>0</v>
       </c>
       <c r="N132">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O132">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P132">
-        <v>11268.54</v>
+        <v>109052.22</v>
       </c>
       <c r="Q132" t="s">
         <v>512</v>
@@ -8122,19 +8122,19 @@
         <v>297</v>
       </c>
       <c r="D133" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E133" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F133" t="s">
-        <v>456</v>
+        <v>507</v>
       </c>
       <c r="H133">
-        <v>912.8282939999998</v>
+        <v>1948.404289679999</v>
       </c>
       <c r="I133">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J133" t="s">
         <v>511</v>
@@ -8143,16 +8143,16 @@
         <v>33</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N133">
         <v>0</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P133">
-        <v>37374.55</v>
+        <v>34603.12</v>
       </c>
       <c r="Q133" t="s">
         <v>512</v>
@@ -8169,19 +8169,19 @@
         <v>297</v>
       </c>
       <c r="D134" t="s">
-        <v>424</v>
+        <v>375</v>
       </c>
       <c r="E134" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F134" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="H134">
-        <v>169.5252546</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I134">
-        <v>234</v>
+        <v>47</v>
       </c>
       <c r="J134" t="s">
         <v>511</v>
@@ -8190,16 +8190,16 @@
         <v>33</v>
       </c>
       <c r="M134">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="N134">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O134">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P134">
-        <v>96453.17</v>
+        <v>69637.41</v>
       </c>
       <c r="Q134" t="s">
         <v>512</v>
@@ -8216,19 +8216,19 @@
         <v>297</v>
       </c>
       <c r="D135" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E135" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="F135" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="H135">
-        <v>871.9473036705882</v>
+        <v>1956.963080117647</v>
       </c>
       <c r="I135">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="J135" t="s">
         <v>511</v>
@@ -8237,16 +8237,16 @@
         <v>33</v>
       </c>
       <c r="M135">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N135">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O135">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="P135">
-        <v>70348.27</v>
+        <v>88079.16</v>
       </c>
       <c r="Q135" t="s">
         <v>512</v>
@@ -8263,19 +8263,19 @@
         <v>297</v>
       </c>
       <c r="D136" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E136" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="F136" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="H136">
-        <v>4934.296426588235</v>
+        <v>874.2436631991176</v>
       </c>
       <c r="I136">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="J136" t="s">
         <v>511</v>
@@ -8284,16 +8284,16 @@
         <v>33</v>
       </c>
       <c r="M136">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N136">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O136">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P136">
-        <v>21111.87</v>
+        <v>59703.68</v>
       </c>
       <c r="Q136" t="s">
         <v>512</v>
@@ -8310,19 +8310,19 @@
         <v>297</v>
       </c>
       <c r="D137" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E137" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F137" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H137">
-        <v>1194.50102472</v>
+        <v>2167.31517804</v>
       </c>
       <c r="I137">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J137" t="s">
         <v>511</v>
@@ -8331,16 +8331,16 @@
         <v>33</v>
       </c>
       <c r="M137">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N137">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="O137">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P137">
-        <v>41216.62</v>
+        <v>94502.95</v>
       </c>
       <c r="Q137" t="s">
         <v>512</v>
@@ -8357,19 +8357,19 @@
         <v>297</v>
       </c>
       <c r="D138" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E138" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F138" t="s">
         <v>508</v>
       </c>
       <c r="H138">
-        <v>2738.484882</v>
+        <v>7169.514799999999</v>
       </c>
       <c r="I138">
-        <v>335</v>
+        <v>11</v>
       </c>
       <c r="J138" t="s">
         <v>511</v>
@@ -8378,16 +8378,16 @@
         <v>33</v>
       </c>
       <c r="M138">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="N138">
+        <v>8</v>
+      </c>
+      <c r="O138">
         <v>2</v>
       </c>
-      <c r="O138">
-        <v>19</v>
-      </c>
       <c r="P138">
-        <v>1275996.17</v>
+        <v>111515.92</v>
       </c>
       <c r="Q138" t="s">
         <v>512</v>
@@ -8404,19 +8404,19 @@
         <v>297</v>
       </c>
       <c r="D139" t="s">
-        <v>429</v>
+        <v>379</v>
       </c>
       <c r="E139" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F139" t="s">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="H139">
-        <v>2261.3068296</v>
+        <v>2803.686903</v>
       </c>
       <c r="I139">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J139" t="s">
         <v>511</v>
@@ -8425,16 +8425,16 @@
         <v>33</v>
       </c>
       <c r="M139">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N139">
         <v>0</v>
       </c>
       <c r="O139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P139">
-        <v>56971.2</v>
+        <v>14763.09</v>
       </c>
       <c r="Q139" t="s">
         <v>512</v>
@@ -8454,16 +8454,16 @@
         <v>430</v>
       </c>
       <c r="E140" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F140" t="s">
-        <v>467</v>
+        <v>509</v>
       </c>
       <c r="H140">
-        <v>1224.499030661912</v>
+        <v>5619.632</v>
       </c>
       <c r="I140">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J140" t="s">
         <v>511</v>
@@ -8472,16 +8472,16 @@
         <v>33</v>
       </c>
       <c r="M140">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N140">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P140">
-        <v>33757.01</v>
+        <v>147521.59</v>
       </c>
       <c r="Q140" t="s">
         <v>512</v>
@@ -8501,16 +8501,16 @@
         <v>431</v>
       </c>
       <c r="E141" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F141" t="s">
         <v>510</v>
       </c>
       <c r="H141">
-        <v>6259.394015999999</v>
+        <v>3129.697008</v>
       </c>
       <c r="I141">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J141" t="s">
         <v>511</v>
@@ -8528,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="P141">
-        <v>142206.19</v>
+        <v>53620.14</v>
       </c>
       <c r="Q141" t="s">
         <v>512</v>
